--- a/codebook_definition.xlsx
+++ b/codebook_definition.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saleh\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anish/Desktop/TSS-Zenodo/tss-interviews-artifacts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BF49FE2-1025-4C69-8FF9-89A296732B66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E909058C-E1BF-8642-8436-AEF329A35F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="definitions" sheetId="1" r:id="rId1"/>
@@ -2356,7 +2356,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2385,12 +2385,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFBDAD7"/>
         <bgColor rgb="FFFBDAD7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA4335"/>
-        <bgColor rgb="FFEA4335"/>
       </patternFill>
     </fill>
     <fill>
@@ -2427,6 +2421,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFB3CEFB"/>
         <bgColor rgb="FFB3CEFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCDAD7"/>
+        <bgColor rgb="FFEA4335"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1F1DB"/>
+        <bgColor rgb="FFFBDAD7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1F1DB"/>
+        <bgColor rgb="FFEA4335"/>
       </patternFill>
     </fill>
   </fills>
@@ -2527,7 +2539,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2556,16 +2568,16 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2578,9 +2590,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2604,18 +2613,51 @@
     <xf numFmtId="49" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2624,37 +2666,13 @@
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2663,6 +2681,12 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFD1F1DB"/>
+      <color rgb="FFFCDAD7"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2877,21 +2901,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K158"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="12.7265625" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="12.6328125" customWidth="1"/>
-    <col min="4" max="4" width="17.7265625" customWidth="1"/>
-    <col min="5" max="5" width="6.90625" customWidth="1"/>
-    <col min="6" max="6" width="17.26953125" customWidth="1"/>
-    <col min="7" max="7" width="29.26953125" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" customWidth="1"/>
+    <col min="5" max="5" width="6.83203125" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" customWidth="1"/>
+    <col min="7" max="7" width="29.33203125" customWidth="1"/>
     <col min="8" max="9" width="28" customWidth="1"/>
-    <col min="10" max="10" width="24.6328125" customWidth="1"/>
-    <col min="11" max="11" width="23.36328125" customWidth="1"/>
+    <col min="10" max="10" width="24.6640625" customWidth="1"/>
+    <col min="11" max="11" width="23.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="28" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2926,17 +2950,17 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="62.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="26">
+    <row r="2" spans="1:11" ht="70" x14ac:dyDescent="0.15">
+      <c r="A2" s="39">
         <v>7</v>
       </c>
-      <c r="B2" s="26">
+      <c r="B2" s="39">
         <v>1</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="39" t="s">
         <v>12</v>
       </c>
       <c r="E2" s="2">
@@ -2957,11 +2981,11 @@
       <c r="J2" s="3"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A3" s="27"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
+    <row r="3" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A3" s="35"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
       <c r="E3" s="2">
         <v>2</v>
       </c>
@@ -2980,11 +3004,11 @@
       <c r="J3" s="3"/>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A4" s="28"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
+    <row r="4" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A4" s="36"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
       <c r="E4" s="2">
         <v>3</v>
       </c>
@@ -3003,17 +3027,17 @@
       <c r="J4" s="3"/>
       <c r="K4" s="2"/>
     </row>
-    <row r="5" spans="1:11" ht="117" x14ac:dyDescent="0.25">
-      <c r="A5" s="35">
+    <row r="5" spans="1:11" ht="126" x14ac:dyDescent="0.15">
+      <c r="A5" s="40">
         <v>46150</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="34">
         <v>2</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D5" s="34" t="s">
         <v>26</v>
       </c>
       <c r="E5" s="4">
@@ -3036,11 +3060,11 @@
       </c>
       <c r="K5" s="4"/>
     </row>
-    <row r="6" spans="1:11" ht="62.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="27"/>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
+    <row r="6" spans="1:11" ht="70" x14ac:dyDescent="0.15">
+      <c r="A6" s="35"/>
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
       <c r="E6" s="4">
         <v>5</v>
       </c>
@@ -3059,11 +3083,11 @@
       <c r="J6" s="5"/>
       <c r="K6" s="4"/>
     </row>
-    <row r="7" spans="1:11" ht="100" x14ac:dyDescent="0.25">
-      <c r="A7" s="27"/>
-      <c r="B7" s="27"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
+    <row r="7" spans="1:11" ht="98" x14ac:dyDescent="0.15">
+      <c r="A7" s="35"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
       <c r="E7" s="4">
         <v>6</v>
       </c>
@@ -3084,11 +3108,11 @@
       </c>
       <c r="K7" s="4"/>
     </row>
-    <row r="8" spans="1:11" ht="62.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="27"/>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
+    <row r="8" spans="1:11" ht="70" x14ac:dyDescent="0.15">
+      <c r="A8" s="35"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
       <c r="E8" s="4">
         <v>7</v>
       </c>
@@ -3107,11 +3131,11 @@
       <c r="J8" s="5"/>
       <c r="K8" s="4"/>
     </row>
-    <row r="9" spans="1:11" ht="78" x14ac:dyDescent="0.25">
-      <c r="A9" s="27"/>
-      <c r="B9" s="27"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
+    <row r="9" spans="1:11" ht="84" x14ac:dyDescent="0.15">
+      <c r="A9" s="35"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
       <c r="E9" s="4">
         <v>8</v>
       </c>
@@ -3132,11 +3156,11 @@
       </c>
       <c r="K9" s="4"/>
     </row>
-    <row r="10" spans="1:11" ht="75" x14ac:dyDescent="0.25">
-      <c r="A10" s="27"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
+    <row r="10" spans="1:11" ht="84" x14ac:dyDescent="0.15">
+      <c r="A10" s="35"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
       <c r="E10" s="4">
         <v>9</v>
       </c>
@@ -3155,11 +3179,11 @@
       <c r="J10" s="5"/>
       <c r="K10" s="4"/>
     </row>
-    <row r="11" spans="1:11" ht="75" x14ac:dyDescent="0.25">
-      <c r="A11" s="27"/>
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
+    <row r="11" spans="1:11" ht="84" x14ac:dyDescent="0.15">
+      <c r="A11" s="35"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
       <c r="E11" s="4">
         <v>10</v>
       </c>
@@ -3178,11 +3202,11 @@
       <c r="J11" s="5"/>
       <c r="K11" s="4"/>
     </row>
-    <row r="12" spans="1:11" ht="100" x14ac:dyDescent="0.25">
-      <c r="A12" s="27"/>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
+    <row r="12" spans="1:11" ht="112" x14ac:dyDescent="0.15">
+      <c r="A12" s="35"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
       <c r="E12" s="4">
         <v>11</v>
       </c>
@@ -3203,11 +3227,11 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="87.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="27"/>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
+    <row r="13" spans="1:11" ht="98" x14ac:dyDescent="0.15">
+      <c r="A13" s="35"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
       <c r="E13" s="4">
         <v>12</v>
       </c>
@@ -3226,11 +3250,11 @@
       <c r="J13" s="5"/>
       <c r="K13" s="4"/>
     </row>
-    <row r="14" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A14" s="28"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
+    <row r="14" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A14" s="36"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
       <c r="E14" s="4">
         <v>13</v>
       </c>
@@ -3249,17 +3273,17 @@
       <c r="J14" s="5"/>
       <c r="K14" s="4"/>
     </row>
-    <row r="15" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="30">
+    <row r="15" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A15" s="37">
         <v>3</v>
       </c>
-      <c r="B15" s="30">
+      <c r="B15" s="37">
         <v>3</v>
       </c>
-      <c r="C15" s="30" t="s">
+      <c r="C15" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="D15" s="30" t="s">
+      <c r="D15" s="37" t="s">
         <v>72</v>
       </c>
       <c r="E15" s="6">
@@ -3280,11 +3304,11 @@
       <c r="J15" s="7"/>
       <c r="K15" s="6"/>
     </row>
-    <row r="16" spans="1:11" ht="25" x14ac:dyDescent="0.25">
-      <c r="A16" s="27"/>
-      <c r="B16" s="27"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
+    <row r="16" spans="1:11" ht="28" x14ac:dyDescent="0.15">
+      <c r="A16" s="35"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
       <c r="E16" s="6">
         <v>15</v>
       </c>
@@ -3303,11 +3327,11 @@
       <c r="J16" s="7"/>
       <c r="K16" s="6"/>
     </row>
-    <row r="17" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A17" s="27"/>
-      <c r="B17" s="27"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
+    <row r="17" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A17" s="35"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
       <c r="E17" s="6">
         <v>16</v>
       </c>
@@ -3326,11 +3350,11 @@
       <c r="J17" s="7"/>
       <c r="K17" s="6"/>
     </row>
-    <row r="18" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="27"/>
-      <c r="B18" s="27"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
+    <row r="18" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A18" s="35"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
       <c r="E18" s="6">
         <v>17</v>
       </c>
@@ -3349,11 +3373,11 @@
       <c r="J18" s="7"/>
       <c r="K18" s="6"/>
     </row>
-    <row r="19" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A19" s="27"/>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
+    <row r="19" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A19" s="35"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
       <c r="E19" s="6">
         <v>18</v>
       </c>
@@ -3372,11 +3396,11 @@
       <c r="J19" s="7"/>
       <c r="K19" s="6"/>
     </row>
-    <row r="20" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="27"/>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
+    <row r="20" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A20" s="35"/>
+      <c r="B20" s="35"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
       <c r="E20" s="6">
         <v>19</v>
       </c>
@@ -3395,11 +3419,11 @@
       <c r="J20" s="7"/>
       <c r="K20" s="6"/>
     </row>
-    <row r="21" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="28"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
+    <row r="21" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A21" s="36"/>
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
       <c r="E21" s="6">
         <v>20</v>
       </c>
@@ -3418,17 +3442,17 @@
       <c r="J21" s="7"/>
       <c r="K21" s="6"/>
     </row>
-    <row r="22" spans="1:11" ht="62.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="31">
+    <row r="22" spans="1:11" ht="70" x14ac:dyDescent="0.15">
+      <c r="A22" s="38">
         <v>3</v>
       </c>
-      <c r="B22" s="31">
+      <c r="B22" s="38">
         <v>4</v>
       </c>
-      <c r="C22" s="31" t="s">
+      <c r="C22" s="38" t="s">
         <v>77</v>
       </c>
-      <c r="D22" s="31" t="s">
+      <c r="D22" s="38" t="s">
         <v>100</v>
       </c>
       <c r="E22" s="8">
@@ -3449,11 +3473,11 @@
       <c r="J22" s="8"/>
       <c r="K22" s="8"/>
     </row>
-    <row r="23" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A23" s="27"/>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
+    <row r="23" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A23" s="35"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
       <c r="E23" s="8">
         <v>22</v>
       </c>
@@ -3472,18 +3496,18 @@
       <c r="J23" s="9"/>
       <c r="K23" s="8"/>
     </row>
-    <row r="24" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="27"/>
-      <c r="B24" s="27"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
+    <row r="24" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A24" s="35"/>
+      <c r="B24" s="35"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="35"/>
       <c r="E24" s="8">
         <v>23</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="F24" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="G24" s="10" t="s">
+      <c r="G24" s="46" t="s">
         <v>110</v>
       </c>
       <c r="H24" s="8" t="s">
@@ -3495,11 +3519,11 @@
       <c r="J24" s="9"/>
       <c r="K24" s="8"/>
     </row>
-    <row r="25" spans="1:11" ht="25" x14ac:dyDescent="0.25">
-      <c r="A25" s="27"/>
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
+    <row r="25" spans="1:11" ht="28" x14ac:dyDescent="0.15">
+      <c r="A25" s="35"/>
+      <c r="B25" s="35"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="35"/>
       <c r="E25" s="8">
         <v>24</v>
       </c>
@@ -3518,11 +3542,11 @@
       <c r="J25" s="9"/>
       <c r="K25" s="8"/>
     </row>
-    <row r="26" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A26" s="27"/>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
+    <row r="26" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A26" s="35"/>
+      <c r="B26" s="35"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="35"/>
       <c r="E26" s="8">
         <v>25</v>
       </c>
@@ -3541,11 +3565,11 @@
       <c r="J26" s="9"/>
       <c r="K26" s="8"/>
     </row>
-    <row r="27" spans="1:11" ht="62.5" x14ac:dyDescent="0.25">
-      <c r="A27" s="27"/>
-      <c r="B27" s="27"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
+    <row r="27" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A27" s="35"/>
+      <c r="B27" s="35"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="35"/>
       <c r="E27" s="8">
         <v>26</v>
       </c>
@@ -3564,11 +3588,11 @@
       <c r="J27" s="9"/>
       <c r="K27" s="8"/>
     </row>
-    <row r="28" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="28"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
+    <row r="28" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A28" s="36"/>
+      <c r="B28" s="36"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
       <c r="E28" s="8">
         <v>27</v>
       </c>
@@ -3587,17 +3611,17 @@
       <c r="J28" s="8"/>
       <c r="K28" s="8"/>
     </row>
-    <row r="29" spans="1:11" ht="100" x14ac:dyDescent="0.25">
-      <c r="A29" s="36">
+    <row r="29" spans="1:11" ht="112" x14ac:dyDescent="0.15">
+      <c r="A29" s="42">
         <v>39116</v>
       </c>
-      <c r="B29" s="26">
+      <c r="B29" s="39">
         <v>5</v>
       </c>
-      <c r="C29" s="26" t="s">
+      <c r="C29" s="39" t="s">
         <v>128</v>
       </c>
-      <c r="D29" s="26" t="s">
+      <c r="D29" s="39" t="s">
         <v>129</v>
       </c>
       <c r="E29" s="2">
@@ -3620,11 +3644,11 @@
       </c>
       <c r="K29" s="2"/>
     </row>
-    <row r="30" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A30" s="27"/>
-      <c r="B30" s="27"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
+    <row r="30" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A30" s="35"/>
+      <c r="B30" s="35"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="35"/>
       <c r="E30" s="2">
         <v>29</v>
       </c>
@@ -3643,11 +3667,11 @@
       <c r="J30" s="3"/>
       <c r="K30" s="2"/>
     </row>
-    <row r="31" spans="1:11" ht="75" x14ac:dyDescent="0.25">
-      <c r="A31" s="27"/>
-      <c r="B31" s="27"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="27"/>
+    <row r="31" spans="1:11" ht="84" x14ac:dyDescent="0.15">
+      <c r="A31" s="35"/>
+      <c r="B31" s="35"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="35"/>
       <c r="E31" s="2">
         <v>30</v>
       </c>
@@ -3666,11 +3690,11 @@
       <c r="J31" s="3"/>
       <c r="K31" s="2"/>
     </row>
-    <row r="32" spans="1:11" ht="87.5" x14ac:dyDescent="0.25">
-      <c r="A32" s="27"/>
-      <c r="B32" s="27"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
+    <row r="32" spans="1:11" ht="98" x14ac:dyDescent="0.15">
+      <c r="A32" s="35"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="35"/>
       <c r="E32" s="2">
         <v>31</v>
       </c>
@@ -3689,11 +3713,11 @@
       <c r="J32" s="3"/>
       <c r="K32" s="2"/>
     </row>
-    <row r="33" spans="1:11" ht="75" x14ac:dyDescent="0.25">
-      <c r="A33" s="27"/>
-      <c r="B33" s="27"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="27"/>
+    <row r="33" spans="1:11" ht="84" x14ac:dyDescent="0.15">
+      <c r="A33" s="35"/>
+      <c r="B33" s="35"/>
+      <c r="C33" s="35"/>
+      <c r="D33" s="35"/>
       <c r="E33" s="2">
         <v>32</v>
       </c>
@@ -3712,11 +3736,11 @@
       <c r="J33" s="3"/>
       <c r="K33" s="2"/>
     </row>
-    <row r="34" spans="1:11" ht="62.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="27"/>
-      <c r="B34" s="27"/>
-      <c r="C34" s="27"/>
-      <c r="D34" s="27"/>
+    <row r="34" spans="1:11" ht="70" x14ac:dyDescent="0.15">
+      <c r="A34" s="35"/>
+      <c r="B34" s="35"/>
+      <c r="C34" s="35"/>
+      <c r="D34" s="35"/>
       <c r="E34" s="2">
         <v>33</v>
       </c>
@@ -3737,11 +3761,11 @@
       </c>
       <c r="K34" s="2"/>
     </row>
-    <row r="35" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A35" s="27"/>
-      <c r="B35" s="27"/>
-      <c r="C35" s="27"/>
-      <c r="D35" s="27"/>
+    <row r="35" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A35" s="35"/>
+      <c r="B35" s="35"/>
+      <c r="C35" s="35"/>
+      <c r="D35" s="35"/>
       <c r="E35" s="2">
         <v>34</v>
       </c>
@@ -3760,11 +3784,11 @@
       <c r="J35" s="3"/>
       <c r="K35" s="2"/>
     </row>
-    <row r="36" spans="1:11" ht="125" x14ac:dyDescent="0.25">
-      <c r="A36" s="28"/>
-      <c r="B36" s="28"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
+    <row r="36" spans="1:11" ht="140" x14ac:dyDescent="0.15">
+      <c r="A36" s="36"/>
+      <c r="B36" s="36"/>
+      <c r="C36" s="36"/>
+      <c r="D36" s="36"/>
       <c r="E36" s="2">
         <v>35</v>
       </c>
@@ -3785,17 +3809,17 @@
       </c>
       <c r="K36" s="2"/>
     </row>
-    <row r="37" spans="1:11" ht="100" x14ac:dyDescent="0.25">
-      <c r="A37" s="35">
+    <row r="37" spans="1:11" ht="112" x14ac:dyDescent="0.15">
+      <c r="A37" s="40">
         <v>46119</v>
       </c>
-      <c r="B37" s="29">
+      <c r="B37" s="34">
         <v>6</v>
       </c>
-      <c r="C37" s="29" t="s">
+      <c r="C37" s="34" t="s">
         <v>165</v>
       </c>
-      <c r="D37" s="29" t="s">
+      <c r="D37" s="34" t="s">
         <v>166</v>
       </c>
       <c r="E37" s="4">
@@ -3816,11 +3840,11 @@
       <c r="J37" s="5"/>
       <c r="K37" s="4"/>
     </row>
-    <row r="38" spans="1:11" ht="175" x14ac:dyDescent="0.25">
-      <c r="A38" s="27"/>
-      <c r="B38" s="27"/>
-      <c r="C38" s="27"/>
-      <c r="D38" s="27"/>
+    <row r="38" spans="1:11" ht="196" x14ac:dyDescent="0.15">
+      <c r="A38" s="35"/>
+      <c r="B38" s="35"/>
+      <c r="C38" s="35"/>
+      <c r="D38" s="35"/>
       <c r="E38" s="4">
         <v>37</v>
       </c>
@@ -3839,11 +3863,11 @@
       <c r="J38" s="5"/>
       <c r="K38" s="4"/>
     </row>
-    <row r="39" spans="1:11" ht="87.5" x14ac:dyDescent="0.25">
-      <c r="A39" s="27"/>
-      <c r="B39" s="27"/>
-      <c r="C39" s="27"/>
-      <c r="D39" s="27"/>
+    <row r="39" spans="1:11" ht="98" x14ac:dyDescent="0.15">
+      <c r="A39" s="35"/>
+      <c r="B39" s="35"/>
+      <c r="C39" s="35"/>
+      <c r="D39" s="35"/>
       <c r="E39" s="4">
         <v>38</v>
       </c>
@@ -3862,11 +3886,11 @@
       <c r="J39" s="5"/>
       <c r="K39" s="4"/>
     </row>
-    <row r="40" spans="1:11" ht="87.5" x14ac:dyDescent="0.25">
-      <c r="A40" s="27"/>
-      <c r="B40" s="27"/>
-      <c r="C40" s="27"/>
-      <c r="D40" s="27"/>
+    <row r="40" spans="1:11" ht="84" x14ac:dyDescent="0.15">
+      <c r="A40" s="35"/>
+      <c r="B40" s="35"/>
+      <c r="C40" s="35"/>
+      <c r="D40" s="35"/>
       <c r="E40" s="4">
         <v>39</v>
       </c>
@@ -3887,11 +3911,11 @@
         <v>183</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="75" x14ac:dyDescent="0.25">
-      <c r="A41" s="27"/>
-      <c r="B41" s="27"/>
-      <c r="C41" s="27"/>
-      <c r="D41" s="27"/>
+    <row r="41" spans="1:11" ht="84" x14ac:dyDescent="0.15">
+      <c r="A41" s="35"/>
+      <c r="B41" s="35"/>
+      <c r="C41" s="35"/>
+      <c r="D41" s="35"/>
       <c r="E41" s="4">
         <v>40</v>
       </c>
@@ -3910,11 +3934,11 @@
       <c r="J41" s="5"/>
       <c r="K41" s="4"/>
     </row>
-    <row r="42" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A42" s="27"/>
-      <c r="B42" s="27"/>
-      <c r="C42" s="27"/>
-      <c r="D42" s="27"/>
+    <row r="42" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A42" s="35"/>
+      <c r="B42" s="35"/>
+      <c r="C42" s="35"/>
+      <c r="D42" s="35"/>
       <c r="E42" s="4">
         <v>41</v>
       </c>
@@ -3933,11 +3957,11 @@
       <c r="J42" s="5"/>
       <c r="K42" s="4"/>
     </row>
-    <row r="43" spans="1:11" ht="75" x14ac:dyDescent="0.25">
-      <c r="A43" s="27"/>
-      <c r="B43" s="27"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
+    <row r="43" spans="1:11" ht="70" x14ac:dyDescent="0.15">
+      <c r="A43" s="35"/>
+      <c r="B43" s="35"/>
+      <c r="C43" s="35"/>
+      <c r="D43" s="35"/>
       <c r="E43" s="4">
         <v>42</v>
       </c>
@@ -3956,11 +3980,11 @@
       <c r="J43" s="5"/>
       <c r="K43" s="4"/>
     </row>
-    <row r="44" spans="1:11" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="A44" s="28"/>
-      <c r="B44" s="28"/>
-      <c r="C44" s="28"/>
-      <c r="D44" s="28"/>
+    <row r="44" spans="1:11" ht="126" x14ac:dyDescent="0.15">
+      <c r="A44" s="36"/>
+      <c r="B44" s="36"/>
+      <c r="C44" s="36"/>
+      <c r="D44" s="36"/>
       <c r="E44" s="4">
         <v>43</v>
       </c>
@@ -3979,17 +4003,17 @@
       <c r="J44" s="5"/>
       <c r="K44" s="4"/>
     </row>
-    <row r="45" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A45" s="37">
+    <row r="45" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A45" s="41">
         <v>38356</v>
       </c>
-      <c r="B45" s="30">
+      <c r="B45" s="37">
         <v>7</v>
       </c>
-      <c r="C45" s="30" t="s">
+      <c r="C45" s="37" t="s">
         <v>200</v>
       </c>
-      <c r="D45" s="30" t="s">
+      <c r="D45" s="37" t="s">
         <v>201</v>
       </c>
       <c r="E45" s="6">
@@ -4010,11 +4034,11 @@
       <c r="J45" s="6"/>
       <c r="K45" s="6"/>
     </row>
-    <row r="46" spans="1:11" ht="125" x14ac:dyDescent="0.25">
-      <c r="A46" s="27"/>
-      <c r="B46" s="27"/>
-      <c r="C46" s="27"/>
-      <c r="D46" s="27"/>
+    <row r="46" spans="1:11" ht="140" x14ac:dyDescent="0.15">
+      <c r="A46" s="35"/>
+      <c r="B46" s="35"/>
+      <c r="C46" s="35"/>
+      <c r="D46" s="35"/>
       <c r="E46" s="6">
         <v>45</v>
       </c>
@@ -4037,11 +4061,11 @@
         <v>211</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="62.5" x14ac:dyDescent="0.25">
-      <c r="A47" s="27"/>
-      <c r="B47" s="27"/>
-      <c r="C47" s="27"/>
-      <c r="D47" s="27"/>
+    <row r="47" spans="1:11" ht="70" x14ac:dyDescent="0.15">
+      <c r="A47" s="35"/>
+      <c r="B47" s="35"/>
+      <c r="C47" s="35"/>
+      <c r="D47" s="35"/>
       <c r="E47" s="6">
         <v>46</v>
       </c>
@@ -4060,11 +4084,11 @@
       <c r="J47" s="6"/>
       <c r="K47" s="6"/>
     </row>
-    <row r="48" spans="1:11" ht="65" x14ac:dyDescent="0.25">
-      <c r="A48" s="27"/>
-      <c r="B48" s="27"/>
-      <c r="C48" s="27"/>
-      <c r="D48" s="27"/>
+    <row r="48" spans="1:11" ht="70" x14ac:dyDescent="0.15">
+      <c r="A48" s="35"/>
+      <c r="B48" s="35"/>
+      <c r="C48" s="35"/>
+      <c r="D48" s="35"/>
       <c r="E48" s="6">
         <v>47</v>
       </c>
@@ -4085,11 +4109,11 @@
       </c>
       <c r="K48" s="6"/>
     </row>
-    <row r="49" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A49" s="27"/>
-      <c r="B49" s="27"/>
-      <c r="C49" s="27"/>
-      <c r="D49" s="27"/>
+    <row r="49" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A49" s="35"/>
+      <c r="B49" s="35"/>
+      <c r="C49" s="35"/>
+      <c r="D49" s="35"/>
       <c r="E49" s="6">
         <v>48</v>
       </c>
@@ -4108,11 +4132,11 @@
       <c r="J49" s="6"/>
       <c r="K49" s="6"/>
     </row>
-    <row r="50" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A50" s="27"/>
-      <c r="B50" s="27"/>
-      <c r="C50" s="27"/>
-      <c r="D50" s="27"/>
+    <row r="50" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A50" s="35"/>
+      <c r="B50" s="35"/>
+      <c r="C50" s="35"/>
+      <c r="D50" s="35"/>
       <c r="E50" s="6">
         <v>49</v>
       </c>
@@ -4131,11 +4155,11 @@
       <c r="J50" s="6"/>
       <c r="K50" s="6"/>
     </row>
-    <row r="51" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A51" s="27"/>
-      <c r="B51" s="27"/>
-      <c r="C51" s="27"/>
-      <c r="D51" s="27"/>
+    <row r="51" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A51" s="35"/>
+      <c r="B51" s="35"/>
+      <c r="C51" s="35"/>
+      <c r="D51" s="35"/>
       <c r="E51" s="6">
         <v>50</v>
       </c>
@@ -4145,7 +4169,7 @@
       <c r="G51" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="H51" s="10" t="s">
+      <c r="H51" s="48" t="s">
         <v>231</v>
       </c>
       <c r="I51" s="6" t="s">
@@ -4154,11 +4178,11 @@
       <c r="J51" s="6"/>
       <c r="K51" s="6"/>
     </row>
-    <row r="52" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A52" s="27"/>
-      <c r="B52" s="27"/>
-      <c r="C52" s="27"/>
-      <c r="D52" s="27"/>
+    <row r="52" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A52" s="35"/>
+      <c r="B52" s="35"/>
+      <c r="C52" s="35"/>
+      <c r="D52" s="35"/>
       <c r="E52" s="6">
         <v>51</v>
       </c>
@@ -4177,11 +4201,11 @@
       <c r="J52" s="6"/>
       <c r="K52" s="6"/>
     </row>
-    <row r="53" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A53" s="27"/>
-      <c r="B53" s="27"/>
-      <c r="C53" s="27"/>
-      <c r="D53" s="27"/>
+    <row r="53" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A53" s="35"/>
+      <c r="B53" s="35"/>
+      <c r="C53" s="35"/>
+      <c r="D53" s="35"/>
       <c r="E53" s="6">
         <v>52</v>
       </c>
@@ -4200,11 +4224,11 @@
       <c r="J53" s="6"/>
       <c r="K53" s="6"/>
     </row>
-    <row r="54" spans="1:11" ht="91" x14ac:dyDescent="0.25">
-      <c r="A54" s="27"/>
-      <c r="B54" s="27"/>
-      <c r="C54" s="27"/>
-      <c r="D54" s="27"/>
+    <row r="54" spans="1:11" ht="98" x14ac:dyDescent="0.15">
+      <c r="A54" s="35"/>
+      <c r="B54" s="35"/>
+      <c r="C54" s="35"/>
+      <c r="D54" s="35"/>
       <c r="E54" s="6">
         <v>53</v>
       </c>
@@ -4225,11 +4249,11 @@
       </c>
       <c r="K54" s="6"/>
     </row>
-    <row r="55" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A55" s="27"/>
-      <c r="B55" s="27"/>
-      <c r="C55" s="27"/>
-      <c r="D55" s="27"/>
+    <row r="55" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A55" s="35"/>
+      <c r="B55" s="35"/>
+      <c r="C55" s="35"/>
+      <c r="D55" s="35"/>
       <c r="E55" s="6">
         <v>54</v>
       </c>
@@ -4252,11 +4276,11 @@
         <v>251</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="62.5" x14ac:dyDescent="0.25">
-      <c r="A56" s="28"/>
-      <c r="B56" s="28"/>
-      <c r="C56" s="28"/>
-      <c r="D56" s="28"/>
+    <row r="56" spans="1:11" ht="70" x14ac:dyDescent="0.15">
+      <c r="A56" s="36"/>
+      <c r="B56" s="36"/>
+      <c r="C56" s="36"/>
+      <c r="D56" s="36"/>
       <c r="E56" s="6">
         <v>55</v>
       </c>
@@ -4275,17 +4299,17 @@
       <c r="J56" s="6"/>
       <c r="K56" s="6"/>
     </row>
-    <row r="57" spans="1:11" ht="62.5" x14ac:dyDescent="0.25">
-      <c r="A57" s="31">
+    <row r="57" spans="1:11" ht="70" x14ac:dyDescent="0.15">
+      <c r="A57" s="38">
         <v>1</v>
       </c>
-      <c r="B57" s="31">
+      <c r="B57" s="38">
         <v>8</v>
       </c>
-      <c r="C57" s="31" t="s">
+      <c r="C57" s="38" t="s">
         <v>256</v>
       </c>
-      <c r="D57" s="31" t="s">
+      <c r="D57" s="38" t="s">
         <v>257</v>
       </c>
       <c r="E57" s="8">
@@ -4308,11 +4332,11 @@
         <v>262</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A58" s="27"/>
-      <c r="B58" s="27"/>
-      <c r="C58" s="27"/>
-      <c r="D58" s="27"/>
+    <row r="58" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A58" s="35"/>
+      <c r="B58" s="35"/>
+      <c r="C58" s="35"/>
+      <c r="D58" s="35"/>
       <c r="E58" s="8">
         <v>57</v>
       </c>
@@ -4331,11 +4355,11 @@
       <c r="J58" s="8"/>
       <c r="K58" s="8"/>
     </row>
-    <row r="59" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A59" s="27"/>
-      <c r="B59" s="27"/>
-      <c r="C59" s="27"/>
-      <c r="D59" s="27"/>
+    <row r="59" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A59" s="35"/>
+      <c r="B59" s="35"/>
+      <c r="C59" s="35"/>
+      <c r="D59" s="35"/>
       <c r="E59" s="8">
         <v>58</v>
       </c>
@@ -4354,11 +4378,11 @@
       <c r="J59" s="8"/>
       <c r="K59" s="8"/>
     </row>
-    <row r="60" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A60" s="27"/>
-      <c r="B60" s="27"/>
-      <c r="C60" s="27"/>
-      <c r="D60" s="27"/>
+    <row r="60" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A60" s="35"/>
+      <c r="B60" s="35"/>
+      <c r="C60" s="35"/>
+      <c r="D60" s="35"/>
       <c r="E60" s="8">
         <v>59</v>
       </c>
@@ -4377,11 +4401,11 @@
       <c r="J60" s="8"/>
       <c r="K60" s="8"/>
     </row>
-    <row r="61" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A61" s="27"/>
-      <c r="B61" s="27"/>
-      <c r="C61" s="27"/>
-      <c r="D61" s="27"/>
+    <row r="61" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A61" s="35"/>
+      <c r="B61" s="35"/>
+      <c r="C61" s="35"/>
+      <c r="D61" s="35"/>
       <c r="E61" s="8">
         <v>60</v>
       </c>
@@ -4400,11 +4424,11 @@
       <c r="J61" s="8"/>
       <c r="K61" s="8"/>
     </row>
-    <row r="62" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A62" s="28"/>
-      <c r="B62" s="28"/>
-      <c r="C62" s="28"/>
-      <c r="D62" s="28"/>
+    <row r="62" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A62" s="36"/>
+      <c r="B62" s="36"/>
+      <c r="C62" s="36"/>
+      <c r="D62" s="36"/>
       <c r="E62" s="8">
         <v>61</v>
       </c>
@@ -4423,17 +4447,17 @@
       <c r="J62" s="8"/>
       <c r="K62" s="8"/>
     </row>
-    <row r="63" spans="1:11" ht="62.5" x14ac:dyDescent="0.25">
-      <c r="A63" s="26">
+    <row r="63" spans="1:11" ht="70" x14ac:dyDescent="0.15">
+      <c r="A63" s="39">
         <v>2</v>
       </c>
-      <c r="B63" s="26">
+      <c r="B63" s="39">
         <v>9</v>
       </c>
-      <c r="C63" s="26" t="s">
+      <c r="C63" s="39" t="s">
         <v>283</v>
       </c>
-      <c r="D63" s="26" t="s">
+      <c r="D63" s="39" t="s">
         <v>284</v>
       </c>
       <c r="E63" s="2">
@@ -4456,11 +4480,11 @@
         <v>289</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A64" s="27"/>
-      <c r="B64" s="27"/>
-      <c r="C64" s="27"/>
-      <c r="D64" s="27"/>
+    <row r="64" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A64" s="35"/>
+      <c r="B64" s="35"/>
+      <c r="C64" s="35"/>
+      <c r="D64" s="35"/>
       <c r="E64" s="2">
         <v>63</v>
       </c>
@@ -4479,11 +4503,11 @@
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
     </row>
-    <row r="65" spans="1:11" ht="62.5" x14ac:dyDescent="0.25">
-      <c r="A65" s="28"/>
-      <c r="B65" s="28"/>
-      <c r="C65" s="28"/>
-      <c r="D65" s="28"/>
+    <row r="65" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A65" s="36"/>
+      <c r="B65" s="36"/>
+      <c r="C65" s="36"/>
+      <c r="D65" s="36"/>
       <c r="E65" s="2">
         <v>64</v>
       </c>
@@ -4502,17 +4526,17 @@
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
     </row>
-    <row r="66" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A66" s="29">
+    <row r="66" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A66" s="34">
         <v>6</v>
       </c>
-      <c r="B66" s="29">
+      <c r="B66" s="34">
         <v>10</v>
       </c>
-      <c r="C66" s="29" t="s">
+      <c r="C66" s="34" t="s">
         <v>298</v>
       </c>
-      <c r="D66" s="29" t="s">
+      <c r="D66" s="34" t="s">
         <v>299</v>
       </c>
       <c r="E66" s="4">
@@ -4533,11 +4557,11 @@
       <c r="J66" s="4"/>
       <c r="K66" s="4"/>
     </row>
-    <row r="67" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A67" s="27"/>
-      <c r="B67" s="27"/>
-      <c r="C67" s="27"/>
-      <c r="D67" s="27"/>
+    <row r="67" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A67" s="35"/>
+      <c r="B67" s="35"/>
+      <c r="C67" s="35"/>
+      <c r="D67" s="35"/>
       <c r="E67" s="4">
         <v>66</v>
       </c>
@@ -4556,11 +4580,11 @@
       <c r="J67" s="4"/>
       <c r="K67" s="4"/>
     </row>
-    <row r="68" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A68" s="27"/>
-      <c r="B68" s="27"/>
-      <c r="C68" s="27"/>
-      <c r="D68" s="27"/>
+    <row r="68" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A68" s="35"/>
+      <c r="B68" s="35"/>
+      <c r="C68" s="35"/>
+      <c r="D68" s="35"/>
       <c r="E68" s="4">
         <v>67</v>
       </c>
@@ -4579,11 +4603,11 @@
       <c r="J68" s="4"/>
       <c r="K68" s="4"/>
     </row>
-    <row r="69" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A69" s="27"/>
-      <c r="B69" s="27"/>
-      <c r="C69" s="27"/>
-      <c r="D69" s="27"/>
+    <row r="69" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A69" s="35"/>
+      <c r="B69" s="35"/>
+      <c r="C69" s="35"/>
+      <c r="D69" s="35"/>
       <c r="E69" s="4">
         <v>68</v>
       </c>
@@ -4602,11 +4626,11 @@
       <c r="J69" s="4"/>
       <c r="K69" s="4"/>
     </row>
-    <row r="70" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A70" s="28"/>
-      <c r="B70" s="28"/>
-      <c r="C70" s="28"/>
-      <c r="D70" s="28"/>
+    <row r="70" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A70" s="36"/>
+      <c r="B70" s="36"/>
+      <c r="C70" s="36"/>
+      <c r="D70" s="36"/>
       <c r="E70" s="4">
         <v>69</v>
       </c>
@@ -4625,17 +4649,17 @@
       <c r="J70" s="4"/>
       <c r="K70" s="4"/>
     </row>
-    <row r="71" spans="1:11" ht="75" x14ac:dyDescent="0.25">
-      <c r="A71" s="30">
+    <row r="71" spans="1:11" ht="84" x14ac:dyDescent="0.15">
+      <c r="A71" s="37">
         <v>3</v>
       </c>
-      <c r="B71" s="30">
+      <c r="B71" s="37">
         <v>11</v>
       </c>
-      <c r="C71" s="30" t="s">
+      <c r="C71" s="37" t="s">
         <v>320</v>
       </c>
-      <c r="D71" s="30" t="s">
+      <c r="D71" s="37" t="s">
         <v>321</v>
       </c>
       <c r="E71" s="6">
@@ -4656,11 +4680,11 @@
       <c r="J71" s="7"/>
       <c r="K71" s="6"/>
     </row>
-    <row r="72" spans="1:11" ht="75" x14ac:dyDescent="0.25">
-      <c r="A72" s="27"/>
-      <c r="B72" s="27"/>
-      <c r="C72" s="27"/>
-      <c r="D72" s="27"/>
+    <row r="72" spans="1:11" ht="84" x14ac:dyDescent="0.15">
+      <c r="A72" s="35"/>
+      <c r="B72" s="35"/>
+      <c r="C72" s="35"/>
+      <c r="D72" s="35"/>
       <c r="E72" s="6">
         <v>71</v>
       </c>
@@ -4679,11 +4703,11 @@
       <c r="J72" s="7"/>
       <c r="K72" s="6"/>
     </row>
-    <row r="73" spans="1:11" ht="75" x14ac:dyDescent="0.25">
-      <c r="A73" s="27"/>
-      <c r="B73" s="27"/>
-      <c r="C73" s="27"/>
-      <c r="D73" s="27"/>
+    <row r="73" spans="1:11" ht="84" x14ac:dyDescent="0.15">
+      <c r="A73" s="35"/>
+      <c r="B73" s="35"/>
+      <c r="C73" s="35"/>
+      <c r="D73" s="35"/>
       <c r="E73" s="6">
         <v>72</v>
       </c>
@@ -4702,11 +4726,11 @@
       <c r="J73" s="7"/>
       <c r="K73" s="6"/>
     </row>
-    <row r="74" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A74" s="27"/>
-      <c r="B74" s="27"/>
-      <c r="C74" s="27"/>
-      <c r="D74" s="27"/>
+    <row r="74" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A74" s="35"/>
+      <c r="B74" s="35"/>
+      <c r="C74" s="35"/>
+      <c r="D74" s="35"/>
       <c r="E74" s="6">
         <v>73</v>
       </c>
@@ -4725,11 +4749,11 @@
       <c r="J74" s="7"/>
       <c r="K74" s="6"/>
     </row>
-    <row r="75" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A75" s="28"/>
-      <c r="B75" s="28"/>
-      <c r="C75" s="28"/>
-      <c r="D75" s="28"/>
+    <row r="75" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A75" s="36"/>
+      <c r="B75" s="36"/>
+      <c r="C75" s="36"/>
+      <c r="D75" s="36"/>
       <c r="E75" s="6">
         <v>74</v>
       </c>
@@ -4748,17 +4772,17 @@
       <c r="J75" s="7"/>
       <c r="K75" s="6"/>
     </row>
-    <row r="76" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A76" s="31">
+    <row r="76" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A76" s="38">
         <v>6</v>
       </c>
-      <c r="B76" s="31">
+      <c r="B76" s="38">
         <v>12</v>
       </c>
-      <c r="C76" s="31" t="s">
+      <c r="C76" s="38" t="s">
         <v>342</v>
       </c>
-      <c r="D76" s="31" t="s">
+      <c r="D76" s="38" t="s">
         <v>343</v>
       </c>
       <c r="E76" s="8">
@@ -4779,11 +4803,11 @@
       <c r="J76" s="9"/>
       <c r="K76" s="8"/>
     </row>
-    <row r="77" spans="1:11" ht="75" x14ac:dyDescent="0.25">
-      <c r="A77" s="27"/>
-      <c r="B77" s="27"/>
-      <c r="C77" s="27"/>
-      <c r="D77" s="27"/>
+    <row r="77" spans="1:11" ht="84" x14ac:dyDescent="0.15">
+      <c r="A77" s="35"/>
+      <c r="B77" s="35"/>
+      <c r="C77" s="35"/>
+      <c r="D77" s="35"/>
       <c r="E77" s="8">
         <v>76</v>
       </c>
@@ -4802,11 +4826,11 @@
       <c r="J77" s="9"/>
       <c r="K77" s="8"/>
     </row>
-    <row r="78" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A78" s="27"/>
-      <c r="B78" s="27"/>
-      <c r="C78" s="27"/>
-      <c r="D78" s="27"/>
+    <row r="78" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A78" s="35"/>
+      <c r="B78" s="35"/>
+      <c r="C78" s="35"/>
+      <c r="D78" s="35"/>
       <c r="E78" s="8">
         <v>77</v>
       </c>
@@ -4825,11 +4849,11 @@
       <c r="J78" s="9"/>
       <c r="K78" s="8"/>
     </row>
-    <row r="79" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A79" s="28"/>
-      <c r="B79" s="28"/>
-      <c r="C79" s="28"/>
-      <c r="D79" s="28"/>
+    <row r="79" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A79" s="36"/>
+      <c r="B79" s="36"/>
+      <c r="C79" s="36"/>
+      <c r="D79" s="36"/>
       <c r="E79" s="8">
         <v>78</v>
       </c>
@@ -4848,17 +4872,17 @@
       <c r="J79" s="9"/>
       <c r="K79" s="8"/>
     </row>
-    <row r="80" spans="1:11" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="A80" s="26">
+    <row r="80" spans="1:11" ht="126" x14ac:dyDescent="0.15">
+      <c r="A80" s="39">
         <v>5</v>
       </c>
-      <c r="B80" s="26">
+      <c r="B80" s="39">
         <v>13</v>
       </c>
-      <c r="C80" s="26" t="s">
+      <c r="C80" s="39" t="s">
         <v>360</v>
       </c>
-      <c r="D80" s="26" t="s">
+      <c r="D80" s="39" t="s">
         <v>361</v>
       </c>
       <c r="E80" s="2">
@@ -4879,11 +4903,11 @@
       <c r="J80" s="2"/>
       <c r="K80" s="2"/>
     </row>
-    <row r="81" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A81" s="27"/>
-      <c r="B81" s="27"/>
-      <c r="C81" s="27"/>
-      <c r="D81" s="27"/>
+    <row r="81" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A81" s="35"/>
+      <c r="B81" s="35"/>
+      <c r="C81" s="35"/>
+      <c r="D81" s="35"/>
       <c r="E81" s="2">
         <v>80</v>
       </c>
@@ -4902,11 +4926,11 @@
       <c r="J81" s="2"/>
       <c r="K81" s="2"/>
     </row>
-    <row r="82" spans="1:11" ht="62.5" x14ac:dyDescent="0.25">
-      <c r="A82" s="27"/>
-      <c r="B82" s="27"/>
-      <c r="C82" s="27"/>
-      <c r="D82" s="27"/>
+    <row r="82" spans="1:11" ht="70" x14ac:dyDescent="0.15">
+      <c r="A82" s="35"/>
+      <c r="B82" s="35"/>
+      <c r="C82" s="35"/>
+      <c r="D82" s="35"/>
       <c r="E82" s="2">
         <v>81</v>
       </c>
@@ -4925,11 +4949,11 @@
       <c r="J82" s="2"/>
       <c r="K82" s="2"/>
     </row>
-    <row r="83" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A83" s="27"/>
-      <c r="B83" s="27"/>
-      <c r="C83" s="27"/>
-      <c r="D83" s="27"/>
+    <row r="83" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A83" s="35"/>
+      <c r="B83" s="35"/>
+      <c r="C83" s="35"/>
+      <c r="D83" s="35"/>
       <c r="E83" s="2">
         <v>82</v>
       </c>
@@ -4948,11 +4972,11 @@
       <c r="J83" s="2"/>
       <c r="K83" s="2"/>
     </row>
-    <row r="84" spans="1:11" ht="62.5" x14ac:dyDescent="0.25">
-      <c r="A84" s="27"/>
-      <c r="B84" s="27"/>
-      <c r="C84" s="27"/>
-      <c r="D84" s="27"/>
+    <row r="84" spans="1:11" ht="70" x14ac:dyDescent="0.15">
+      <c r="A84" s="35"/>
+      <c r="B84" s="35"/>
+      <c r="C84" s="35"/>
+      <c r="D84" s="35"/>
       <c r="E84" s="2">
         <v>83</v>
       </c>
@@ -4971,11 +4995,11 @@
       <c r="J84" s="2"/>
       <c r="K84" s="2"/>
     </row>
-    <row r="85" spans="1:11" ht="62.5" x14ac:dyDescent="0.25">
-      <c r="A85" s="27"/>
-      <c r="B85" s="27"/>
-      <c r="C85" s="27"/>
-      <c r="D85" s="27"/>
+    <row r="85" spans="1:11" ht="70" x14ac:dyDescent="0.15">
+      <c r="A85" s="35"/>
+      <c r="B85" s="35"/>
+      <c r="C85" s="35"/>
+      <c r="D85" s="35"/>
       <c r="E85" s="2">
         <v>84</v>
       </c>
@@ -4994,11 +5018,11 @@
       <c r="J85" s="2"/>
       <c r="K85" s="2"/>
     </row>
-    <row r="86" spans="1:11" ht="75" x14ac:dyDescent="0.25">
-      <c r="A86" s="27"/>
-      <c r="B86" s="27"/>
-      <c r="C86" s="27"/>
-      <c r="D86" s="27"/>
+    <row r="86" spans="1:11" ht="84" x14ac:dyDescent="0.15">
+      <c r="A86" s="35"/>
+      <c r="B86" s="35"/>
+      <c r="C86" s="35"/>
+      <c r="D86" s="35"/>
       <c r="E86" s="2">
         <v>85</v>
       </c>
@@ -5017,11 +5041,11 @@
       <c r="J86" s="2"/>
       <c r="K86" s="2"/>
     </row>
-    <row r="87" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A87" s="28"/>
-      <c r="B87" s="28"/>
-      <c r="C87" s="28"/>
-      <c r="D87" s="28"/>
+    <row r="87" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A87" s="36"/>
+      <c r="B87" s="36"/>
+      <c r="C87" s="36"/>
+      <c r="D87" s="36"/>
       <c r="E87" s="2">
         <v>86</v>
       </c>
@@ -5040,17 +5064,17 @@
       <c r="J87" s="2"/>
       <c r="K87" s="2"/>
     </row>
-    <row r="88" spans="1:11" ht="62.5" x14ac:dyDescent="0.25">
-      <c r="A88" s="29">
+    <row r="88" spans="1:11" ht="70" x14ac:dyDescent="0.15">
+      <c r="A88" s="34">
         <v>6</v>
       </c>
-      <c r="B88" s="29">
+      <c r="B88" s="34">
         <v>14</v>
       </c>
-      <c r="C88" s="29" t="s">
+      <c r="C88" s="34" t="s">
         <v>392</v>
       </c>
-      <c r="D88" s="29" t="s">
+      <c r="D88" s="34" t="s">
         <v>393</v>
       </c>
       <c r="E88" s="4">
@@ -5071,11 +5095,11 @@
       <c r="J88" s="4"/>
       <c r="K88" s="4"/>
     </row>
-    <row r="89" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A89" s="27"/>
-      <c r="B89" s="27"/>
-      <c r="C89" s="27"/>
-      <c r="D89" s="27"/>
+    <row r="89" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A89" s="35"/>
+      <c r="B89" s="35"/>
+      <c r="C89" s="35"/>
+      <c r="D89" s="35"/>
       <c r="E89" s="4">
         <v>88</v>
       </c>
@@ -5094,11 +5118,11 @@
       <c r="J89" s="4"/>
       <c r="K89" s="4"/>
     </row>
-    <row r="90" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A90" s="27"/>
-      <c r="B90" s="27"/>
-      <c r="C90" s="27"/>
-      <c r="D90" s="27"/>
+    <row r="90" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A90" s="35"/>
+      <c r="B90" s="35"/>
+      <c r="C90" s="35"/>
+      <c r="D90" s="35"/>
       <c r="E90" s="4">
         <v>89</v>
       </c>
@@ -5117,11 +5141,11 @@
       <c r="J90" s="4"/>
       <c r="K90" s="4"/>
     </row>
-    <row r="91" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A91" s="27"/>
-      <c r="B91" s="27"/>
-      <c r="C91" s="27"/>
-      <c r="D91" s="27"/>
+    <row r="91" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A91" s="35"/>
+      <c r="B91" s="35"/>
+      <c r="C91" s="35"/>
+      <c r="D91" s="35"/>
       <c r="E91" s="4">
         <v>90</v>
       </c>
@@ -5140,11 +5164,11 @@
       <c r="J91" s="4"/>
       <c r="K91" s="4"/>
     </row>
-    <row r="92" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A92" s="27"/>
-      <c r="B92" s="27"/>
-      <c r="C92" s="27"/>
-      <c r="D92" s="27"/>
+    <row r="92" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A92" s="35"/>
+      <c r="B92" s="35"/>
+      <c r="C92" s="35"/>
+      <c r="D92" s="35"/>
       <c r="E92" s="4">
         <v>91</v>
       </c>
@@ -5163,11 +5187,11 @@
       <c r="J92" s="4"/>
       <c r="K92" s="4"/>
     </row>
-    <row r="93" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A93" s="27"/>
-      <c r="B93" s="27"/>
-      <c r="C93" s="27"/>
-      <c r="D93" s="27"/>
+    <row r="93" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A93" s="35"/>
+      <c r="B93" s="35"/>
+      <c r="C93" s="35"/>
+      <c r="D93" s="35"/>
       <c r="E93" s="4">
         <v>92</v>
       </c>
@@ -5186,11 +5210,11 @@
       <c r="J93" s="4"/>
       <c r="K93" s="4"/>
     </row>
-    <row r="94" spans="1:11" ht="62.5" x14ac:dyDescent="0.25">
-      <c r="A94" s="28"/>
-      <c r="B94" s="28"/>
-      <c r="C94" s="28"/>
-      <c r="D94" s="28"/>
+    <row r="94" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A94" s="36"/>
+      <c r="B94" s="36"/>
+      <c r="C94" s="36"/>
+      <c r="D94" s="36"/>
       <c r="E94" s="4">
         <v>93</v>
       </c>
@@ -5209,17 +5233,17 @@
       <c r="J94" s="4"/>
       <c r="K94" s="4"/>
     </row>
-    <row r="95" spans="1:11" ht="62.5" x14ac:dyDescent="0.25">
-      <c r="A95" s="32">
+    <row r="95" spans="1:11" ht="70" x14ac:dyDescent="0.15">
+      <c r="A95" s="44">
         <v>46117</v>
       </c>
-      <c r="B95" s="30">
+      <c r="B95" s="37">
         <v>15</v>
       </c>
-      <c r="C95" s="30" t="s">
+      <c r="C95" s="37" t="s">
         <v>422</v>
       </c>
-      <c r="D95" s="30" t="s">
+      <c r="D95" s="37" t="s">
         <v>423</v>
       </c>
       <c r="E95" s="6">
@@ -5240,11 +5264,11 @@
       <c r="J95" s="6"/>
       <c r="K95" s="6"/>
     </row>
-    <row r="96" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A96" s="27"/>
-      <c r="B96" s="27"/>
-      <c r="C96" s="27"/>
-      <c r="D96" s="27"/>
+    <row r="96" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A96" s="35"/>
+      <c r="B96" s="35"/>
+      <c r="C96" s="35"/>
+      <c r="D96" s="35"/>
       <c r="E96" s="6">
         <v>95</v>
       </c>
@@ -5263,11 +5287,11 @@
       <c r="J96" s="6"/>
       <c r="K96" s="6"/>
     </row>
-    <row r="97" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A97" s="27"/>
-      <c r="B97" s="27"/>
-      <c r="C97" s="27"/>
-      <c r="D97" s="27"/>
+    <row r="97" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A97" s="35"/>
+      <c r="B97" s="35"/>
+      <c r="C97" s="35"/>
+      <c r="D97" s="35"/>
       <c r="E97" s="6">
         <v>96</v>
       </c>
@@ -5286,11 +5310,11 @@
       <c r="J97" s="6"/>
       <c r="K97" s="6"/>
     </row>
-    <row r="98" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A98" s="28"/>
-      <c r="B98" s="28"/>
-      <c r="C98" s="28"/>
-      <c r="D98" s="28"/>
+    <row r="98" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A98" s="36"/>
+      <c r="B98" s="36"/>
+      <c r="C98" s="36"/>
+      <c r="D98" s="36"/>
       <c r="E98" s="6">
         <v>97</v>
       </c>
@@ -5309,17 +5333,17 @@
       <c r="J98" s="6"/>
       <c r="K98" s="6"/>
     </row>
-    <row r="99" spans="1:11" ht="62.5" x14ac:dyDescent="0.25">
-      <c r="A99" s="33">
+    <row r="99" spans="1:11" ht="70" x14ac:dyDescent="0.15">
+      <c r="A99" s="45">
         <v>46150</v>
       </c>
-      <c r="B99" s="31">
+      <c r="B99" s="38">
         <v>16</v>
       </c>
-      <c r="C99" s="31" t="s">
+      <c r="C99" s="38" t="s">
         <v>440</v>
       </c>
-      <c r="D99" s="31" t="s">
+      <c r="D99" s="38" t="s">
         <v>441</v>
       </c>
       <c r="E99" s="8">
@@ -5340,11 +5364,11 @@
       <c r="J99" s="9"/>
       <c r="K99" s="8"/>
     </row>
-    <row r="100" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A100" s="28"/>
-      <c r="B100" s="28"/>
-      <c r="C100" s="28"/>
-      <c r="D100" s="28"/>
+    <row r="100" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A100" s="36"/>
+      <c r="B100" s="36"/>
+      <c r="C100" s="36"/>
+      <c r="D100" s="36"/>
       <c r="E100" s="8">
         <v>99</v>
       </c>
@@ -5363,17 +5387,17 @@
       <c r="J100" s="9"/>
       <c r="K100" s="8"/>
     </row>
-    <row r="101" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A101" s="26">
+    <row r="101" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A101" s="39">
         <v>4</v>
       </c>
-      <c r="B101" s="26">
+      <c r="B101" s="39">
         <v>17</v>
       </c>
-      <c r="C101" s="26" t="s">
+      <c r="C101" s="39" t="s">
         <v>450</v>
       </c>
-      <c r="D101" s="26" t="s">
+      <c r="D101" s="39" t="s">
         <v>451</v>
       </c>
       <c r="E101" s="2">
@@ -5394,11 +5418,11 @@
       <c r="J101" s="2"/>
       <c r="K101" s="2"/>
     </row>
-    <row r="102" spans="1:11" ht="75" x14ac:dyDescent="0.25">
-      <c r="A102" s="27"/>
-      <c r="B102" s="27"/>
-      <c r="C102" s="27"/>
-      <c r="D102" s="27"/>
+    <row r="102" spans="1:11" ht="84" x14ac:dyDescent="0.15">
+      <c r="A102" s="35"/>
+      <c r="B102" s="35"/>
+      <c r="C102" s="35"/>
+      <c r="D102" s="35"/>
       <c r="E102" s="2">
         <v>101</v>
       </c>
@@ -5417,11 +5441,11 @@
       <c r="J102" s="2"/>
       <c r="K102" s="2"/>
     </row>
-    <row r="103" spans="1:11" ht="62.5" x14ac:dyDescent="0.25">
-      <c r="A103" s="27"/>
-      <c r="B103" s="27"/>
-      <c r="C103" s="27"/>
-      <c r="D103" s="27"/>
+    <row r="103" spans="1:11" ht="70" x14ac:dyDescent="0.15">
+      <c r="A103" s="35"/>
+      <c r="B103" s="35"/>
+      <c r="C103" s="35"/>
+      <c r="D103" s="35"/>
       <c r="E103" s="2">
         <v>102</v>
       </c>
@@ -5440,11 +5464,11 @@
       <c r="J103" s="2"/>
       <c r="K103" s="2"/>
     </row>
-    <row r="104" spans="1:11" ht="75" x14ac:dyDescent="0.25">
-      <c r="A104" s="27"/>
-      <c r="B104" s="27"/>
-      <c r="C104" s="27"/>
-      <c r="D104" s="27"/>
+    <row r="104" spans="1:11" ht="84" x14ac:dyDescent="0.15">
+      <c r="A104" s="35"/>
+      <c r="B104" s="35"/>
+      <c r="C104" s="35"/>
+      <c r="D104" s="35"/>
       <c r="E104" s="2">
         <v>103</v>
       </c>
@@ -5463,11 +5487,11 @@
       <c r="J104" s="2"/>
       <c r="K104" s="2"/>
     </row>
-    <row r="105" spans="1:11" ht="75" x14ac:dyDescent="0.25">
-      <c r="A105" s="28"/>
-      <c r="B105" s="28"/>
-      <c r="C105" s="28"/>
-      <c r="D105" s="28"/>
+    <row r="105" spans="1:11" ht="84" x14ac:dyDescent="0.15">
+      <c r="A105" s="36"/>
+      <c r="B105" s="36"/>
+      <c r="C105" s="36"/>
+      <c r="D105" s="36"/>
       <c r="E105" s="2">
         <v>104</v>
       </c>
@@ -5486,17 +5510,17 @@
       <c r="J105" s="2"/>
       <c r="K105" s="2"/>
     </row>
-    <row r="106" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A106" s="29">
+    <row r="106" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A106" s="34">
         <v>4</v>
       </c>
-      <c r="B106" s="29">
+      <c r="B106" s="34">
         <v>18</v>
       </c>
-      <c r="C106" s="29" t="s">
+      <c r="C106" s="34" t="s">
         <v>472</v>
       </c>
-      <c r="D106" s="29" t="s">
+      <c r="D106" s="34" t="s">
         <v>473</v>
       </c>
       <c r="E106" s="4">
@@ -5517,11 +5541,11 @@
       <c r="J106" s="5"/>
       <c r="K106" s="4"/>
     </row>
-    <row r="107" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A107" s="27"/>
-      <c r="B107" s="27"/>
-      <c r="C107" s="27"/>
-      <c r="D107" s="27"/>
+    <row r="107" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A107" s="35"/>
+      <c r="B107" s="35"/>
+      <c r="C107" s="35"/>
+      <c r="D107" s="35"/>
       <c r="E107" s="4">
         <v>106</v>
       </c>
@@ -5540,11 +5564,11 @@
       <c r="J107" s="5"/>
       <c r="K107" s="4"/>
     </row>
-    <row r="108" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A108" s="27"/>
-      <c r="B108" s="27"/>
-      <c r="C108" s="27"/>
-      <c r="D108" s="27"/>
+    <row r="108" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A108" s="35"/>
+      <c r="B108" s="35"/>
+      <c r="C108" s="35"/>
+      <c r="D108" s="35"/>
       <c r="E108" s="4">
         <v>107</v>
       </c>
@@ -5563,11 +5587,11 @@
       <c r="J108" s="5"/>
       <c r="K108" s="4"/>
     </row>
-    <row r="109" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A109" s="27"/>
-      <c r="B109" s="27"/>
-      <c r="C109" s="27"/>
-      <c r="D109" s="27"/>
+    <row r="109" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A109" s="35"/>
+      <c r="B109" s="35"/>
+      <c r="C109" s="35"/>
+      <c r="D109" s="35"/>
       <c r="E109" s="4">
         <v>108</v>
       </c>
@@ -5586,11 +5610,11 @@
       <c r="J109" s="5"/>
       <c r="K109" s="4"/>
     </row>
-    <row r="110" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A110" s="27"/>
-      <c r="B110" s="27"/>
-      <c r="C110" s="27"/>
-      <c r="D110" s="27"/>
+    <row r="110" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A110" s="35"/>
+      <c r="B110" s="35"/>
+      <c r="C110" s="35"/>
+      <c r="D110" s="35"/>
       <c r="E110" s="4">
         <v>109</v>
       </c>
@@ -5609,11 +5633,11 @@
       <c r="J110" s="5"/>
       <c r="K110" s="4"/>
     </row>
-    <row r="111" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A111" s="28"/>
-      <c r="B111" s="28"/>
-      <c r="C111" s="28"/>
-      <c r="D111" s="28"/>
+    <row r="111" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A111" s="36"/>
+      <c r="B111" s="36"/>
+      <c r="C111" s="36"/>
+      <c r="D111" s="36"/>
       <c r="E111" s="4">
         <v>110</v>
       </c>
@@ -5632,17 +5656,17 @@
       <c r="J111" s="5"/>
       <c r="K111" s="4"/>
     </row>
-    <row r="112" spans="1:11" ht="75" x14ac:dyDescent="0.25">
-      <c r="A112" s="30">
+    <row r="112" spans="1:11" ht="84" x14ac:dyDescent="0.15">
+      <c r="A112" s="37">
         <v>2</v>
       </c>
-      <c r="B112" s="30">
+      <c r="B112" s="37">
         <v>19</v>
       </c>
-      <c r="C112" s="30" t="s">
+      <c r="C112" s="37" t="s">
         <v>498</v>
       </c>
-      <c r="D112" s="30" t="s">
+      <c r="D112" s="37" t="s">
         <v>499</v>
       </c>
       <c r="E112" s="6">
@@ -5663,11 +5687,11 @@
       <c r="J112" s="7"/>
       <c r="K112" s="6"/>
     </row>
-    <row r="113" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A113" s="27"/>
-      <c r="B113" s="27"/>
-      <c r="C113" s="27"/>
-      <c r="D113" s="27"/>
+    <row r="113" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A113" s="35"/>
+      <c r="B113" s="35"/>
+      <c r="C113" s="35"/>
+      <c r="D113" s="35"/>
       <c r="E113" s="6">
         <v>112</v>
       </c>
@@ -5686,11 +5710,11 @@
       <c r="J113" s="7"/>
       <c r="K113" s="6"/>
     </row>
-    <row r="114" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A114" s="28"/>
-      <c r="B114" s="28"/>
-      <c r="C114" s="28"/>
-      <c r="D114" s="28"/>
+    <row r="114" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A114" s="36"/>
+      <c r="B114" s="36"/>
+      <c r="C114" s="36"/>
+      <c r="D114" s="36"/>
       <c r="E114" s="6">
         <v>113</v>
       </c>
@@ -5709,17 +5733,17 @@
       <c r="J114" s="7"/>
       <c r="K114" s="6"/>
     </row>
-    <row r="115" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A115" s="31">
+    <row r="115" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A115" s="38">
         <v>2</v>
       </c>
-      <c r="B115" s="31">
+      <c r="B115" s="38">
         <v>20</v>
       </c>
-      <c r="C115" s="31" t="s">
+      <c r="C115" s="38" t="s">
         <v>512</v>
       </c>
-      <c r="D115" s="31" t="s">
+      <c r="D115" s="38" t="s">
         <v>513</v>
       </c>
       <c r="E115" s="8">
@@ -5740,11 +5764,11 @@
       <c r="J115" s="9"/>
       <c r="K115" s="8"/>
     </row>
-    <row r="116" spans="1:11" ht="75" x14ac:dyDescent="0.25">
-      <c r="A116" s="27"/>
-      <c r="B116" s="27"/>
-      <c r="C116" s="27"/>
-      <c r="D116" s="27"/>
+    <row r="116" spans="1:11" ht="84" x14ac:dyDescent="0.15">
+      <c r="A116" s="35"/>
+      <c r="B116" s="35"/>
+      <c r="C116" s="35"/>
+      <c r="D116" s="35"/>
       <c r="E116" s="8">
         <v>115</v>
       </c>
@@ -5763,11 +5787,11 @@
       <c r="J116" s="9"/>
       <c r="K116" s="8"/>
     </row>
-    <row r="117" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A117" s="27"/>
-      <c r="B117" s="27"/>
-      <c r="C117" s="27"/>
-      <c r="D117" s="27"/>
+    <row r="117" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A117" s="35"/>
+      <c r="B117" s="35"/>
+      <c r="C117" s="35"/>
+      <c r="D117" s="35"/>
       <c r="E117" s="8">
         <v>116</v>
       </c>
@@ -5786,11 +5810,11 @@
       <c r="J117" s="9"/>
       <c r="K117" s="8"/>
     </row>
-    <row r="118" spans="1:11" ht="75" x14ac:dyDescent="0.25">
-      <c r="A118" s="27"/>
-      <c r="B118" s="27"/>
-      <c r="C118" s="27"/>
-      <c r="D118" s="27"/>
+    <row r="118" spans="1:11" ht="84" x14ac:dyDescent="0.15">
+      <c r="A118" s="35"/>
+      <c r="B118" s="35"/>
+      <c r="C118" s="35"/>
+      <c r="D118" s="35"/>
       <c r="E118" s="8">
         <v>117</v>
       </c>
@@ -5809,11 +5833,11 @@
       <c r="J118" s="9"/>
       <c r="K118" s="8"/>
     </row>
-    <row r="119" spans="1:11" ht="87.5" x14ac:dyDescent="0.25">
-      <c r="A119" s="27"/>
-      <c r="B119" s="27"/>
-      <c r="C119" s="27"/>
-      <c r="D119" s="27"/>
+    <row r="119" spans="1:11" ht="98" x14ac:dyDescent="0.15">
+      <c r="A119" s="35"/>
+      <c r="B119" s="35"/>
+      <c r="C119" s="35"/>
+      <c r="D119" s="35"/>
       <c r="E119" s="8">
         <v>118</v>
       </c>
@@ -5832,11 +5856,11 @@
       <c r="J119" s="9"/>
       <c r="K119" s="8"/>
     </row>
-    <row r="120" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A120" s="27"/>
-      <c r="B120" s="27"/>
-      <c r="C120" s="27"/>
-      <c r="D120" s="27"/>
+    <row r="120" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A120" s="35"/>
+      <c r="B120" s="35"/>
+      <c r="C120" s="35"/>
+      <c r="D120" s="35"/>
       <c r="E120" s="8">
         <v>119</v>
       </c>
@@ -5855,11 +5879,11 @@
       <c r="J120" s="9"/>
       <c r="K120" s="8"/>
     </row>
-    <row r="121" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A121" s="28"/>
-      <c r="B121" s="28"/>
-      <c r="C121" s="28"/>
-      <c r="D121" s="28"/>
+    <row r="121" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A121" s="36"/>
+      <c r="B121" s="36"/>
+      <c r="C121" s="36"/>
+      <c r="D121" s="36"/>
       <c r="E121" s="8">
         <v>120</v>
       </c>
@@ -5878,17 +5902,17 @@
       <c r="J121" s="9"/>
       <c r="K121" s="8"/>
     </row>
-    <row r="122" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A122" s="34">
+    <row r="122" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A122" s="43">
         <v>46117</v>
       </c>
-      <c r="B122" s="26">
+      <c r="B122" s="39">
         <v>21</v>
       </c>
-      <c r="C122" s="26" t="s">
+      <c r="C122" s="39" t="s">
         <v>540</v>
       </c>
-      <c r="D122" s="26" t="s">
+      <c r="D122" s="39" t="s">
         <v>541</v>
       </c>
       <c r="E122" s="2">
@@ -5909,11 +5933,11 @@
       <c r="J122" s="3"/>
       <c r="K122" s="2"/>
     </row>
-    <row r="123" spans="1:11" ht="62.5" x14ac:dyDescent="0.25">
-      <c r="A123" s="27"/>
-      <c r="B123" s="27"/>
-      <c r="C123" s="27"/>
-      <c r="D123" s="27"/>
+    <row r="123" spans="1:11" ht="70" x14ac:dyDescent="0.15">
+      <c r="A123" s="35"/>
+      <c r="B123" s="35"/>
+      <c r="C123" s="35"/>
+      <c r="D123" s="35"/>
       <c r="E123" s="2">
         <v>122</v>
       </c>
@@ -5932,11 +5956,11 @@
       <c r="J123" s="3"/>
       <c r="K123" s="2"/>
     </row>
-    <row r="124" spans="1:11" ht="62.5" x14ac:dyDescent="0.25">
-      <c r="A124" s="27"/>
-      <c r="B124" s="27"/>
-      <c r="C124" s="27"/>
-      <c r="D124" s="27"/>
+    <row r="124" spans="1:11" ht="70" x14ac:dyDescent="0.15">
+      <c r="A124" s="35"/>
+      <c r="B124" s="35"/>
+      <c r="C124" s="35"/>
+      <c r="D124" s="35"/>
       <c r="E124" s="2">
         <v>123</v>
       </c>
@@ -5955,11 +5979,11 @@
       <c r="J124" s="3"/>
       <c r="K124" s="2"/>
     </row>
-    <row r="125" spans="1:11" ht="62.5" x14ac:dyDescent="0.25">
-      <c r="A125" s="27"/>
-      <c r="B125" s="27"/>
-      <c r="C125" s="27"/>
-      <c r="D125" s="27"/>
+    <row r="125" spans="1:11" ht="70" x14ac:dyDescent="0.15">
+      <c r="A125" s="35"/>
+      <c r="B125" s="35"/>
+      <c r="C125" s="35"/>
+      <c r="D125" s="35"/>
       <c r="E125" s="2">
         <v>124</v>
       </c>
@@ -5978,11 +6002,11 @@
       <c r="J125" s="3"/>
       <c r="K125" s="2"/>
     </row>
-    <row r="126" spans="1:11" ht="62.5" x14ac:dyDescent="0.25">
-      <c r="A126" s="27"/>
-      <c r="B126" s="27"/>
-      <c r="C126" s="27"/>
-      <c r="D126" s="27"/>
+    <row r="126" spans="1:11" ht="70" x14ac:dyDescent="0.15">
+      <c r="A126" s="35"/>
+      <c r="B126" s="35"/>
+      <c r="C126" s="35"/>
+      <c r="D126" s="35"/>
       <c r="E126" s="2">
         <v>125</v>
       </c>
@@ -6001,11 +6025,11 @@
       <c r="J126" s="3"/>
       <c r="K126" s="2"/>
     </row>
-    <row r="127" spans="1:11" ht="62.5" x14ac:dyDescent="0.25">
-      <c r="A127" s="27"/>
-      <c r="B127" s="27"/>
-      <c r="C127" s="27"/>
-      <c r="D127" s="27"/>
+    <row r="127" spans="1:11" ht="70" x14ac:dyDescent="0.15">
+      <c r="A127" s="35"/>
+      <c r="B127" s="35"/>
+      <c r="C127" s="35"/>
+      <c r="D127" s="35"/>
       <c r="E127" s="2">
         <v>126</v>
       </c>
@@ -6024,11 +6048,11 @@
       <c r="J127" s="3"/>
       <c r="K127" s="2"/>
     </row>
-    <row r="128" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A128" s="28"/>
-      <c r="B128" s="28"/>
-      <c r="C128" s="28"/>
-      <c r="D128" s="28"/>
+    <row r="128" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A128" s="36"/>
+      <c r="B128" s="36"/>
+      <c r="C128" s="36"/>
+      <c r="D128" s="36"/>
       <c r="E128" s="2">
         <v>127</v>
       </c>
@@ -6047,17 +6071,17 @@
       <c r="J128" s="3"/>
       <c r="K128" s="2"/>
     </row>
-    <row r="129" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A129" s="29">
+    <row r="129" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A129" s="34">
         <v>6</v>
       </c>
-      <c r="B129" s="29">
+      <c r="B129" s="34">
         <v>22</v>
       </c>
-      <c r="C129" s="29" t="s">
+      <c r="C129" s="34" t="s">
         <v>569</v>
       </c>
-      <c r="D129" s="29" t="s">
+      <c r="D129" s="34" t="s">
         <v>570</v>
       </c>
       <c r="E129" s="4">
@@ -6078,11 +6102,11 @@
       <c r="J129" s="5"/>
       <c r="K129" s="4"/>
     </row>
-    <row r="130" spans="1:11" ht="62.5" x14ac:dyDescent="0.25">
-      <c r="A130" s="27"/>
-      <c r="B130" s="27"/>
-      <c r="C130" s="27"/>
-      <c r="D130" s="27"/>
+    <row r="130" spans="1:11" ht="70" x14ac:dyDescent="0.15">
+      <c r="A130" s="35"/>
+      <c r="B130" s="35"/>
+      <c r="C130" s="35"/>
+      <c r="D130" s="35"/>
       <c r="E130" s="4">
         <v>129</v>
       </c>
@@ -6101,11 +6125,11 @@
       <c r="J130" s="5"/>
       <c r="K130" s="4"/>
     </row>
-    <row r="131" spans="1:11" ht="75" x14ac:dyDescent="0.25">
-      <c r="A131" s="27"/>
-      <c r="B131" s="27"/>
-      <c r="C131" s="27"/>
-      <c r="D131" s="27"/>
+    <row r="131" spans="1:11" ht="70" x14ac:dyDescent="0.15">
+      <c r="A131" s="35"/>
+      <c r="B131" s="35"/>
+      <c r="C131" s="35"/>
+      <c r="D131" s="35"/>
       <c r="E131" s="4">
         <v>130</v>
       </c>
@@ -6124,11 +6148,11 @@
       <c r="J131" s="5"/>
       <c r="K131" s="4"/>
     </row>
-    <row r="132" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A132" s="28"/>
-      <c r="B132" s="28"/>
-      <c r="C132" s="28"/>
-      <c r="D132" s="28"/>
+    <row r="132" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A132" s="36"/>
+      <c r="B132" s="36"/>
+      <c r="C132" s="36"/>
+      <c r="D132" s="36"/>
       <c r="E132" s="4">
         <v>131</v>
       </c>
@@ -6147,17 +6171,17 @@
       <c r="J132" s="5"/>
       <c r="K132" s="4"/>
     </row>
-    <row r="133" spans="1:11" ht="87.5" x14ac:dyDescent="0.25">
-      <c r="A133" s="30">
+    <row r="133" spans="1:11" ht="98" x14ac:dyDescent="0.15">
+      <c r="A133" s="37">
         <v>3</v>
       </c>
-      <c r="B133" s="30">
+      <c r="B133" s="37">
         <v>23</v>
       </c>
-      <c r="C133" s="30" t="s">
+      <c r="C133" s="37" t="s">
         <v>587</v>
       </c>
-      <c r="D133" s="30" t="s">
+      <c r="D133" s="37" t="s">
         <v>588</v>
       </c>
       <c r="E133" s="6">
@@ -6178,11 +6202,11 @@
       <c r="J133" s="7"/>
       <c r="K133" s="6"/>
     </row>
-    <row r="134" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A134" s="27"/>
-      <c r="B134" s="27"/>
-      <c r="C134" s="27"/>
-      <c r="D134" s="27"/>
+    <row r="134" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A134" s="35"/>
+      <c r="B134" s="35"/>
+      <c r="C134" s="35"/>
+      <c r="D134" s="35"/>
       <c r="E134" s="6">
         <v>133</v>
       </c>
@@ -6201,11 +6225,11 @@
       <c r="J134" s="7"/>
       <c r="K134" s="6"/>
     </row>
-    <row r="135" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A135" s="27"/>
-      <c r="B135" s="27"/>
-      <c r="C135" s="27"/>
-      <c r="D135" s="27"/>
+    <row r="135" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A135" s="35"/>
+      <c r="B135" s="35"/>
+      <c r="C135" s="35"/>
+      <c r="D135" s="35"/>
       <c r="E135" s="6">
         <v>134</v>
       </c>
@@ -6224,21 +6248,21 @@
       <c r="J135" s="7"/>
       <c r="K135" s="6"/>
     </row>
-    <row r="136" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A136" s="27"/>
-      <c r="B136" s="27"/>
-      <c r="C136" s="27"/>
-      <c r="D136" s="27"/>
+    <row r="136" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A136" s="35"/>
+      <c r="B136" s="35"/>
+      <c r="C136" s="35"/>
+      <c r="D136" s="35"/>
       <c r="E136" s="6">
         <v>135</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>601</v>
       </c>
-      <c r="G136" s="10" t="s">
+      <c r="G136" s="48" t="s">
         <v>602</v>
       </c>
-      <c r="H136" s="10" t="s">
+      <c r="H136" s="48" t="s">
         <v>603</v>
       </c>
       <c r="I136" s="6" t="s">
@@ -6247,11 +6271,11 @@
       <c r="J136" s="7"/>
       <c r="K136" s="6"/>
     </row>
-    <row r="137" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A137" s="27"/>
-      <c r="B137" s="27"/>
-      <c r="C137" s="27"/>
-      <c r="D137" s="27"/>
+    <row r="137" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A137" s="35"/>
+      <c r="B137" s="35"/>
+      <c r="C137" s="35"/>
+      <c r="D137" s="35"/>
       <c r="E137" s="6">
         <v>136</v>
       </c>
@@ -6270,11 +6294,11 @@
       <c r="J137" s="7"/>
       <c r="K137" s="6"/>
     </row>
-    <row r="138" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A138" s="27"/>
-      <c r="B138" s="27"/>
-      <c r="C138" s="27"/>
-      <c r="D138" s="27"/>
+    <row r="138" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A138" s="35"/>
+      <c r="B138" s="35"/>
+      <c r="C138" s="35"/>
+      <c r="D138" s="35"/>
       <c r="E138" s="6">
         <v>137</v>
       </c>
@@ -6293,11 +6317,11 @@
       <c r="J138" s="7"/>
       <c r="K138" s="6"/>
     </row>
-    <row r="139" spans="1:11" ht="62.5" x14ac:dyDescent="0.25">
-      <c r="A139" s="27"/>
-      <c r="B139" s="27"/>
-      <c r="C139" s="27"/>
-      <c r="D139" s="27"/>
+    <row r="139" spans="1:11" ht="70" x14ac:dyDescent="0.15">
+      <c r="A139" s="35"/>
+      <c r="B139" s="35"/>
+      <c r="C139" s="35"/>
+      <c r="D139" s="35"/>
       <c r="E139" s="6">
         <v>138</v>
       </c>
@@ -6316,11 +6340,11 @@
       <c r="J139" s="7"/>
       <c r="K139" s="6"/>
     </row>
-    <row r="140" spans="1:11" ht="100" x14ac:dyDescent="0.25">
-      <c r="A140" s="28"/>
-      <c r="B140" s="28"/>
-      <c r="C140" s="28"/>
-      <c r="D140" s="28"/>
+    <row r="140" spans="1:11" ht="112" x14ac:dyDescent="0.15">
+      <c r="A140" s="36"/>
+      <c r="B140" s="36"/>
+      <c r="C140" s="36"/>
+      <c r="D140" s="36"/>
       <c r="E140" s="6">
         <v>139</v>
       </c>
@@ -6341,17 +6365,17 @@
         <v>621</v>
       </c>
     </row>
-    <row r="141" spans="1:11" ht="87.5" x14ac:dyDescent="0.25">
-      <c r="A141" s="31">
+    <row r="141" spans="1:11" ht="98" x14ac:dyDescent="0.15">
+      <c r="A141" s="38">
         <v>2</v>
       </c>
-      <c r="B141" s="31">
+      <c r="B141" s="38">
         <v>24</v>
       </c>
-      <c r="C141" s="31" t="s">
+      <c r="C141" s="38" t="s">
         <v>583</v>
       </c>
-      <c r="D141" s="31" t="s">
+      <c r="D141" s="38" t="s">
         <v>622</v>
       </c>
       <c r="E141" s="8">
@@ -6372,11 +6396,11 @@
       <c r="J141" s="9"/>
       <c r="K141" s="8"/>
     </row>
-    <row r="142" spans="1:11" ht="87.5" x14ac:dyDescent="0.25">
-      <c r="A142" s="27"/>
-      <c r="B142" s="27"/>
-      <c r="C142" s="27"/>
-      <c r="D142" s="27"/>
+    <row r="142" spans="1:11" ht="98" x14ac:dyDescent="0.15">
+      <c r="A142" s="35"/>
+      <c r="B142" s="35"/>
+      <c r="C142" s="35"/>
+      <c r="D142" s="35"/>
       <c r="E142" s="8">
         <v>141</v>
       </c>
@@ -6395,11 +6419,11 @@
       <c r="J142" s="9"/>
       <c r="K142" s="8"/>
     </row>
-    <row r="143" spans="1:11" ht="75" x14ac:dyDescent="0.25">
-      <c r="A143" s="28"/>
-      <c r="B143" s="28"/>
-      <c r="C143" s="28"/>
-      <c r="D143" s="28"/>
+    <row r="143" spans="1:11" ht="84" x14ac:dyDescent="0.15">
+      <c r="A143" s="36"/>
+      <c r="B143" s="36"/>
+      <c r="C143" s="36"/>
+      <c r="D143" s="36"/>
       <c r="E143" s="8">
         <v>142</v>
       </c>
@@ -6418,17 +6442,17 @@
       <c r="J143" s="9"/>
       <c r="K143" s="8"/>
     </row>
-    <row r="144" spans="1:11" ht="62.5" x14ac:dyDescent="0.25">
-      <c r="A144" s="26">
+    <row r="144" spans="1:11" ht="70" x14ac:dyDescent="0.15">
+      <c r="A144" s="39">
         <v>2</v>
       </c>
-      <c r="B144" s="26">
+      <c r="B144" s="39">
         <v>25</v>
       </c>
-      <c r="C144" s="26" t="s">
+      <c r="C144" s="39" t="s">
         <v>635</v>
       </c>
-      <c r="D144" s="26" t="s">
+      <c r="D144" s="39" t="s">
         <v>636</v>
       </c>
       <c r="E144" s="2">
@@ -6451,11 +6475,11 @@
         <v>641</v>
       </c>
     </row>
-    <row r="145" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A145" s="27"/>
-      <c r="B145" s="27"/>
-      <c r="C145" s="27"/>
-      <c r="D145" s="27"/>
+    <row r="145" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A145" s="35"/>
+      <c r="B145" s="35"/>
+      <c r="C145" s="35"/>
+      <c r="D145" s="35"/>
       <c r="E145" s="2">
         <v>144</v>
       </c>
@@ -6476,11 +6500,11 @@
         <v>646</v>
       </c>
     </row>
-    <row r="146" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A146" s="27"/>
-      <c r="B146" s="27"/>
-      <c r="C146" s="27"/>
-      <c r="D146" s="27"/>
+    <row r="146" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A146" s="35"/>
+      <c r="B146" s="35"/>
+      <c r="C146" s="35"/>
+      <c r="D146" s="35"/>
       <c r="E146" s="2">
         <v>145</v>
       </c>
@@ -6499,11 +6523,11 @@
       <c r="J146" s="2"/>
       <c r="K146" s="2"/>
     </row>
-    <row r="147" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A147" s="27"/>
-      <c r="B147" s="27"/>
-      <c r="C147" s="27"/>
-      <c r="D147" s="27"/>
+    <row r="147" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A147" s="35"/>
+      <c r="B147" s="35"/>
+      <c r="C147" s="35"/>
+      <c r="D147" s="35"/>
       <c r="E147" s="2">
         <v>146</v>
       </c>
@@ -6522,11 +6546,11 @@
       <c r="J147" s="3"/>
       <c r="K147" s="2"/>
     </row>
-    <row r="148" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A148" s="27"/>
-      <c r="B148" s="27"/>
-      <c r="C148" s="27"/>
-      <c r="D148" s="27"/>
+    <row r="148" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A148" s="35"/>
+      <c r="B148" s="35"/>
+      <c r="C148" s="35"/>
+      <c r="D148" s="35"/>
       <c r="E148" s="2">
         <v>147</v>
       </c>
@@ -6545,11 +6569,11 @@
       <c r="J148" s="3"/>
       <c r="K148" s="2"/>
     </row>
-    <row r="149" spans="1:11" ht="62.5" x14ac:dyDescent="0.25">
-      <c r="A149" s="28"/>
-      <c r="B149" s="28"/>
-      <c r="C149" s="28"/>
-      <c r="D149" s="28"/>
+    <row r="149" spans="1:11" ht="70" x14ac:dyDescent="0.15">
+      <c r="A149" s="36"/>
+      <c r="B149" s="36"/>
+      <c r="C149" s="36"/>
+      <c r="D149" s="36"/>
       <c r="E149" s="2">
         <v>148</v>
       </c>
@@ -6568,17 +6592,17 @@
       <c r="J149" s="3"/>
       <c r="K149" s="2"/>
     </row>
-    <row r="150" spans="1:11" ht="87.5" x14ac:dyDescent="0.25">
-      <c r="A150" s="35">
+    <row r="150" spans="1:11" ht="98" x14ac:dyDescent="0.15">
+      <c r="A150" s="40">
         <v>46180</v>
       </c>
-      <c r="B150" s="29">
+      <c r="B150" s="34">
         <v>26</v>
       </c>
-      <c r="C150" s="29" t="s">
+      <c r="C150" s="34" t="s">
         <v>663</v>
       </c>
-      <c r="D150" s="29" t="s">
+      <c r="D150" s="34" t="s">
         <v>664</v>
       </c>
       <c r="E150" s="4">
@@ -6599,11 +6623,11 @@
       <c r="J150" s="5"/>
       <c r="K150" s="4"/>
     </row>
-    <row r="151" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A151" s="27"/>
-      <c r="B151" s="27"/>
-      <c r="C151" s="27"/>
-      <c r="D151" s="27"/>
+    <row r="151" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A151" s="35"/>
+      <c r="B151" s="35"/>
+      <c r="C151" s="35"/>
+      <c r="D151" s="35"/>
       <c r="E151" s="4">
         <v>150</v>
       </c>
@@ -6622,11 +6646,11 @@
       <c r="J151" s="5"/>
       <c r="K151" s="4"/>
     </row>
-    <row r="152" spans="1:11" ht="62.5" x14ac:dyDescent="0.25">
-      <c r="A152" s="27"/>
-      <c r="B152" s="27"/>
-      <c r="C152" s="27"/>
-      <c r="D152" s="27"/>
+    <row r="152" spans="1:11" ht="70" x14ac:dyDescent="0.15">
+      <c r="A152" s="35"/>
+      <c r="B152" s="35"/>
+      <c r="C152" s="35"/>
+      <c r="D152" s="35"/>
       <c r="E152" s="4">
         <v>151</v>
       </c>
@@ -6645,11 +6669,11 @@
       <c r="J152" s="5"/>
       <c r="K152" s="4"/>
     </row>
-    <row r="153" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A153" s="28"/>
-      <c r="B153" s="28"/>
-      <c r="C153" s="28"/>
-      <c r="D153" s="28"/>
+    <row r="153" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A153" s="36"/>
+      <c r="B153" s="36"/>
+      <c r="C153" s="36"/>
+      <c r="D153" s="36"/>
       <c r="E153" s="4">
         <v>152</v>
       </c>
@@ -6668,17 +6692,17 @@
       <c r="J153" s="5"/>
       <c r="K153" s="4"/>
     </row>
-    <row r="154" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A154" s="30">
+    <row r="154" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A154" s="37">
         <v>1</v>
       </c>
-      <c r="B154" s="30">
+      <c r="B154" s="37">
         <v>27</v>
       </c>
-      <c r="C154" s="30" t="s">
+      <c r="C154" s="37" t="s">
         <v>680</v>
       </c>
-      <c r="D154" s="30" t="s">
+      <c r="D154" s="37" t="s">
         <v>681</v>
       </c>
       <c r="E154" s="6">
@@ -6699,11 +6723,11 @@
       <c r="J154" s="7"/>
       <c r="K154" s="6"/>
     </row>
-    <row r="155" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A155" s="27"/>
-      <c r="B155" s="27"/>
-      <c r="C155" s="27"/>
-      <c r="D155" s="27"/>
+    <row r="155" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A155" s="35"/>
+      <c r="B155" s="35"/>
+      <c r="C155" s="35"/>
+      <c r="D155" s="35"/>
       <c r="E155" s="6">
         <v>154</v>
       </c>
@@ -6722,11 +6746,11 @@
       <c r="J155" s="7"/>
       <c r="K155" s="6"/>
     </row>
-    <row r="156" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A156" s="27"/>
-      <c r="B156" s="27"/>
-      <c r="C156" s="27"/>
-      <c r="D156" s="27"/>
+    <row r="156" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A156" s="35"/>
+      <c r="B156" s="35"/>
+      <c r="C156" s="35"/>
+      <c r="D156" s="35"/>
       <c r="E156" s="6">
         <v>155</v>
       </c>
@@ -6745,11 +6769,11 @@
       <c r="J156" s="7"/>
       <c r="K156" s="6"/>
     </row>
-    <row r="157" spans="1:11" ht="50" x14ac:dyDescent="0.25">
-      <c r="A157" s="27"/>
-      <c r="B157" s="27"/>
-      <c r="C157" s="27"/>
-      <c r="D157" s="27"/>
+    <row r="157" spans="1:11" ht="56" x14ac:dyDescent="0.15">
+      <c r="A157" s="35"/>
+      <c r="B157" s="35"/>
+      <c r="C157" s="35"/>
+      <c r="D157" s="35"/>
       <c r="E157" s="6">
         <v>156</v>
       </c>
@@ -6768,11 +6792,11 @@
       <c r="J157" s="7"/>
       <c r="K157" s="6"/>
     </row>
-    <row r="158" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A158" s="28"/>
-      <c r="B158" s="28"/>
-      <c r="C158" s="28"/>
-      <c r="D158" s="28"/>
+    <row r="158" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A158" s="36"/>
+      <c r="B158" s="36"/>
+      <c r="C158" s="36"/>
+      <c r="D158" s="36"/>
       <c r="E158" s="6">
         <v>157</v>
       </c>
@@ -6793,34 +6817,62 @@
     </row>
   </sheetData>
   <mergeCells count="108">
-    <mergeCell ref="B150:B153"/>
-    <mergeCell ref="C150:C153"/>
-    <mergeCell ref="A154:A158"/>
-    <mergeCell ref="B154:B158"/>
-    <mergeCell ref="C154:C158"/>
-    <mergeCell ref="D154:D158"/>
-    <mergeCell ref="B141:B143"/>
-    <mergeCell ref="C141:C143"/>
-    <mergeCell ref="A144:A149"/>
-    <mergeCell ref="B144:B149"/>
-    <mergeCell ref="C144:C149"/>
-    <mergeCell ref="D144:D149"/>
-    <mergeCell ref="A150:A153"/>
-    <mergeCell ref="D150:D153"/>
-    <mergeCell ref="C29:C36"/>
-    <mergeCell ref="D29:D36"/>
-    <mergeCell ref="B37:B44"/>
-    <mergeCell ref="C37:C44"/>
-    <mergeCell ref="D37:D44"/>
-    <mergeCell ref="C57:C62"/>
-    <mergeCell ref="D57:D62"/>
-    <mergeCell ref="A37:A44"/>
-    <mergeCell ref="A45:A56"/>
-    <mergeCell ref="B45:B56"/>
-    <mergeCell ref="C45:C56"/>
-    <mergeCell ref="D45:D56"/>
-    <mergeCell ref="A57:A62"/>
-    <mergeCell ref="B57:B62"/>
+    <mergeCell ref="A63:A65"/>
+    <mergeCell ref="B63:B65"/>
+    <mergeCell ref="C63:C65"/>
+    <mergeCell ref="D63:D65"/>
+    <mergeCell ref="B66:B70"/>
+    <mergeCell ref="C66:C70"/>
+    <mergeCell ref="D66:D70"/>
+    <mergeCell ref="A66:A70"/>
+    <mergeCell ref="A71:A75"/>
+    <mergeCell ref="B71:B75"/>
+    <mergeCell ref="C71:C75"/>
+    <mergeCell ref="D71:D75"/>
+    <mergeCell ref="A76:A79"/>
+    <mergeCell ref="B76:B79"/>
+    <mergeCell ref="B88:B94"/>
+    <mergeCell ref="C88:C94"/>
+    <mergeCell ref="C76:C79"/>
+    <mergeCell ref="D76:D79"/>
+    <mergeCell ref="A80:A87"/>
+    <mergeCell ref="B80:B87"/>
+    <mergeCell ref="C80:C87"/>
+    <mergeCell ref="D80:D87"/>
+    <mergeCell ref="D88:D94"/>
+    <mergeCell ref="C99:C100"/>
+    <mergeCell ref="D99:D100"/>
+    <mergeCell ref="A88:A94"/>
+    <mergeCell ref="A95:A98"/>
+    <mergeCell ref="B95:B98"/>
+    <mergeCell ref="C95:C98"/>
+    <mergeCell ref="D95:D98"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="A101:A105"/>
+    <mergeCell ref="B101:B105"/>
+    <mergeCell ref="C101:C105"/>
+    <mergeCell ref="D101:D105"/>
+    <mergeCell ref="B106:B111"/>
+    <mergeCell ref="C106:C111"/>
+    <mergeCell ref="D106:D111"/>
+    <mergeCell ref="A106:A111"/>
+    <mergeCell ref="A112:A114"/>
+    <mergeCell ref="B112:B114"/>
+    <mergeCell ref="C112:C114"/>
+    <mergeCell ref="D112:D114"/>
+    <mergeCell ref="A115:A121"/>
+    <mergeCell ref="B115:B121"/>
+    <mergeCell ref="C115:C121"/>
+    <mergeCell ref="D115:D121"/>
+    <mergeCell ref="A122:A128"/>
+    <mergeCell ref="B122:B128"/>
+    <mergeCell ref="C122:C128"/>
+    <mergeCell ref="D122:D128"/>
+    <mergeCell ref="A129:A132"/>
+    <mergeCell ref="D129:D132"/>
+    <mergeCell ref="B129:B132"/>
+    <mergeCell ref="C129:C132"/>
     <mergeCell ref="A133:A140"/>
     <mergeCell ref="B133:B140"/>
     <mergeCell ref="C133:C140"/>
@@ -6845,62 +6897,34 @@
     <mergeCell ref="B22:B28"/>
     <mergeCell ref="A29:A36"/>
     <mergeCell ref="B29:B36"/>
-    <mergeCell ref="A115:A121"/>
-    <mergeCell ref="B115:B121"/>
-    <mergeCell ref="C115:C121"/>
-    <mergeCell ref="D115:D121"/>
-    <mergeCell ref="A122:A128"/>
-    <mergeCell ref="B122:B128"/>
-    <mergeCell ref="C122:C128"/>
-    <mergeCell ref="D122:D128"/>
-    <mergeCell ref="A129:A132"/>
-    <mergeCell ref="D129:D132"/>
-    <mergeCell ref="B129:B132"/>
-    <mergeCell ref="C129:C132"/>
-    <mergeCell ref="A101:A105"/>
-    <mergeCell ref="B101:B105"/>
-    <mergeCell ref="C101:C105"/>
-    <mergeCell ref="D101:D105"/>
-    <mergeCell ref="B106:B111"/>
-    <mergeCell ref="C106:C111"/>
-    <mergeCell ref="D106:D111"/>
-    <mergeCell ref="A106:A111"/>
-    <mergeCell ref="A112:A114"/>
-    <mergeCell ref="B112:B114"/>
-    <mergeCell ref="C112:C114"/>
-    <mergeCell ref="D112:D114"/>
-    <mergeCell ref="C99:C100"/>
-    <mergeCell ref="D99:D100"/>
-    <mergeCell ref="A88:A94"/>
-    <mergeCell ref="A95:A98"/>
-    <mergeCell ref="B95:B98"/>
-    <mergeCell ref="C95:C98"/>
-    <mergeCell ref="D95:D98"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="A76:A79"/>
-    <mergeCell ref="B76:B79"/>
-    <mergeCell ref="B88:B94"/>
-    <mergeCell ref="C88:C94"/>
-    <mergeCell ref="C76:C79"/>
-    <mergeCell ref="D76:D79"/>
-    <mergeCell ref="A80:A87"/>
-    <mergeCell ref="B80:B87"/>
-    <mergeCell ref="C80:C87"/>
-    <mergeCell ref="D80:D87"/>
-    <mergeCell ref="D88:D94"/>
-    <mergeCell ref="A63:A65"/>
-    <mergeCell ref="B63:B65"/>
-    <mergeCell ref="C63:C65"/>
-    <mergeCell ref="D63:D65"/>
-    <mergeCell ref="B66:B70"/>
-    <mergeCell ref="C66:C70"/>
-    <mergeCell ref="D66:D70"/>
-    <mergeCell ref="A66:A70"/>
-    <mergeCell ref="A71:A75"/>
-    <mergeCell ref="B71:B75"/>
-    <mergeCell ref="C71:C75"/>
-    <mergeCell ref="D71:D75"/>
+    <mergeCell ref="C29:C36"/>
+    <mergeCell ref="D29:D36"/>
+    <mergeCell ref="B37:B44"/>
+    <mergeCell ref="C37:C44"/>
+    <mergeCell ref="D37:D44"/>
+    <mergeCell ref="C57:C62"/>
+    <mergeCell ref="D57:D62"/>
+    <mergeCell ref="A37:A44"/>
+    <mergeCell ref="A45:A56"/>
+    <mergeCell ref="B45:B56"/>
+    <mergeCell ref="C45:C56"/>
+    <mergeCell ref="D45:D56"/>
+    <mergeCell ref="A57:A62"/>
+    <mergeCell ref="B57:B62"/>
+    <mergeCell ref="B150:B153"/>
+    <mergeCell ref="C150:C153"/>
+    <mergeCell ref="A154:A158"/>
+    <mergeCell ref="B154:B158"/>
+    <mergeCell ref="C154:C158"/>
+    <mergeCell ref="D154:D158"/>
+    <mergeCell ref="B141:B143"/>
+    <mergeCell ref="C141:C143"/>
+    <mergeCell ref="A144:A149"/>
+    <mergeCell ref="B144:B149"/>
+    <mergeCell ref="C144:C149"/>
+    <mergeCell ref="D144:D149"/>
+    <mergeCell ref="A150:A153"/>
+    <mergeCell ref="D150:D153"/>
   </mergeCells>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -6915,691 +6939,684 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F49"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="10.90625" customWidth="1"/>
-    <col min="2" max="2" width="14.6328125" customWidth="1"/>
-    <col min="3" max="3" width="23.26953125" customWidth="1"/>
-    <col min="4" max="4" width="32.453125" customWidth="1"/>
-    <col min="5" max="6" width="42.26953125" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="23.33203125" customWidth="1"/>
+    <col min="4" max="4" width="32.5" customWidth="1"/>
+    <col min="5" max="6" width="42.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A1" s="28" t="s">
         <v>702</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+    </row>
+    <row r="2" spans="1:6" ht="14" x14ac:dyDescent="0.15">
+      <c r="A2" s="11" t="s">
         <v>703</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="11" t="s">
         <v>704</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="11" t="s">
         <v>705</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="11" t="s">
         <v>706</v>
       </c>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12" t="s">
+      <c r="E2" s="11"/>
+      <c r="F2" s="11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="25" x14ac:dyDescent="0.25">
-      <c r="A3" s="12">
+    <row r="3" spans="1:6" ht="28" x14ac:dyDescent="0.15">
+      <c r="A3" s="11">
         <v>1</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>707</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="11" t="s">
         <v>708</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="11" t="s">
         <v>709</v>
       </c>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12" t="s">
+      <c r="E3" s="11"/>
+      <c r="F3" s="11" t="s">
         <v>710</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="50" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
+    <row r="4" spans="1:6" ht="56" x14ac:dyDescent="0.15">
+      <c r="A4" s="11">
         <v>2</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="11" t="s">
         <v>711</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>712</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>713</v>
       </c>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12" t="s">
+      <c r="E4" s="11"/>
+      <c r="F4" s="11" t="s">
         <v>714</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="25" x14ac:dyDescent="0.25">
-      <c r="A5" s="12">
+    <row r="5" spans="1:6" ht="28" x14ac:dyDescent="0.15">
+      <c r="A5" s="11">
         <v>3</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="11" t="s">
         <v>715</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="11" t="s">
         <v>716</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="11" t="s">
         <v>717</v>
       </c>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12" t="s">
+      <c r="E5" s="11"/>
+      <c r="F5" s="11" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="50" x14ac:dyDescent="0.25">
-      <c r="A6" s="12">
+    <row r="6" spans="1:6" ht="56" x14ac:dyDescent="0.15">
+      <c r="A6" s="11">
         <v>4</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="11" t="s">
         <v>720</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="11" t="s">
         <v>721</v>
       </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12" t="s">
+      <c r="E6" s="11"/>
+      <c r="F6" s="11" t="s">
         <v>722</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="13"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="13"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="43" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A8" s="12"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A9" s="28" t="s">
         <v>723</v>
       </c>
-      <c r="B9" s="44"/>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+    </row>
+    <row r="10" spans="1:6" ht="14" x14ac:dyDescent="0.15">
+      <c r="A10" s="13" t="s">
         <v>724</v>
       </c>
-      <c r="B10" s="46" t="s">
+      <c r="B10" s="30" t="s">
         <v>725</v>
       </c>
-      <c r="C10" s="39"/>
-      <c r="D10" s="46" t="s">
+      <c r="C10" s="27"/>
+      <c r="D10" s="30" t="s">
         <v>726</v>
       </c>
-      <c r="E10" s="45"/>
-      <c r="F10" s="39"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="15">
+      <c r="E10" s="26"/>
+      <c r="F10" s="27"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A11" s="14">
         <v>1</v>
       </c>
-      <c r="B11" s="42" t="s">
+      <c r="B11" s="31" t="s">
         <v>727</v>
       </c>
-      <c r="C11" s="39"/>
-      <c r="D11" s="42" t="s">
+      <c r="C11" s="27"/>
+      <c r="D11" s="31" t="s">
         <v>728</v>
       </c>
-      <c r="E11" s="45"/>
-      <c r="F11" s="39"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="16">
+      <c r="E11" s="26"/>
+      <c r="F11" s="27"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A12" s="15">
         <v>2</v>
       </c>
-      <c r="B12" s="38" t="s">
+      <c r="B12" s="25" t="s">
         <v>729</v>
       </c>
-      <c r="C12" s="39"/>
-      <c r="D12" s="38" t="s">
+      <c r="C12" s="27"/>
+      <c r="D12" s="25" t="s">
         <v>730</v>
       </c>
-      <c r="E12" s="45"/>
-      <c r="F12" s="39"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="17">
+      <c r="E12" s="26"/>
+      <c r="F12" s="27"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A13" s="16">
         <v>3</v>
       </c>
-      <c r="B13" s="40" t="s">
+      <c r="B13" s="32" t="s">
         <v>731</v>
       </c>
-      <c r="C13" s="39"/>
-      <c r="D13" s="40" t="s">
+      <c r="C13" s="27"/>
+      <c r="D13" s="32" t="s">
         <v>732</v>
       </c>
-      <c r="E13" s="45"/>
-      <c r="F13" s="39"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="18">
+      <c r="E13" s="26"/>
+      <c r="F13" s="27"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A14" s="17">
         <v>4</v>
       </c>
-      <c r="B14" s="41" t="s">
+      <c r="B14" s="33" t="s">
         <v>733</v>
       </c>
-      <c r="C14" s="39"/>
-      <c r="D14" s="41" t="s">
+      <c r="C14" s="27"/>
+      <c r="D14" s="33" t="s">
         <v>734</v>
       </c>
-      <c r="E14" s="45"/>
-      <c r="F14" s="39"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="15">
+      <c r="E14" s="26"/>
+      <c r="F14" s="27"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A15" s="14">
         <v>5</v>
       </c>
-      <c r="B15" s="42" t="s">
+      <c r="B15" s="31" t="s">
         <v>735</v>
       </c>
-      <c r="C15" s="39"/>
-      <c r="D15" s="42" t="s">
+      <c r="C15" s="27"/>
+      <c r="D15" s="31" t="s">
         <v>736</v>
       </c>
-      <c r="E15" s="45"/>
-      <c r="F15" s="39"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="16">
+      <c r="E15" s="26"/>
+      <c r="F15" s="27"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A16" s="15">
         <v>6</v>
       </c>
-      <c r="B16" s="38" t="s">
+      <c r="B16" s="25" t="s">
         <v>737</v>
       </c>
-      <c r="C16" s="39"/>
-      <c r="D16" s="38" t="s">
+      <c r="C16" s="27"/>
+      <c r="D16" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="E16" s="45"/>
-      <c r="F16" s="39"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="17">
+      <c r="E16" s="26"/>
+      <c r="F16" s="27"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A17" s="16">
         <v>7</v>
       </c>
-      <c r="B17" s="40" t="s">
+      <c r="B17" s="32" t="s">
         <v>739</v>
       </c>
-      <c r="C17" s="39"/>
-      <c r="D17" s="40" t="s">
+      <c r="C17" s="27"/>
+      <c r="D17" s="32" t="s">
         <v>740</v>
       </c>
-      <c r="E17" s="45"/>
-      <c r="F17" s="39"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="18">
+      <c r="E17" s="26"/>
+      <c r="F17" s="27"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A18" s="17">
         <v>8</v>
       </c>
-      <c r="B18" s="41" t="s">
+      <c r="B18" s="33" t="s">
         <v>741</v>
       </c>
-      <c r="C18" s="39"/>
-      <c r="D18" s="41" t="s">
+      <c r="C18" s="27"/>
+      <c r="D18" s="33" t="s">
         <v>742</v>
       </c>
-      <c r="E18" s="45"/>
-      <c r="F18" s="39"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="19"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="19"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-    </row>
-    <row r="21" spans="1:6" ht="13" x14ac:dyDescent="0.25">
-      <c r="A21" s="43" t="s">
+      <c r="E18" s="26"/>
+      <c r="F18" s="27"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A21" s="28" t="s">
         <v>743</v>
       </c>
-      <c r="B21" s="44"/>
-      <c r="C21" s="44"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-    </row>
-    <row r="22" spans="1:6" ht="13" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
+      <c r="B21" s="29"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+    </row>
+    <row r="22" spans="1:6" ht="14" x14ac:dyDescent="0.15">
+      <c r="A22" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="13" t="s">
         <v>744</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C22" s="13" t="s">
         <v>745</v>
       </c>
-      <c r="D22" s="21"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="21"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D22" s="20"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="20"/>
+    </row>
+    <row r="23" spans="1:6" ht="14" x14ac:dyDescent="0.15">
       <c r="A23" s="2">
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="22" t="s">
+      <c r="C23" s="21" t="s">
         <v>746</v>
       </c>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+    </row>
+    <row r="24" spans="1:6" ht="14" x14ac:dyDescent="0.15">
       <c r="A24" s="4">
         <v>2</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="23" t="s">
+      <c r="C24" s="22" t="s">
         <v>747</v>
       </c>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+    </row>
+    <row r="25" spans="1:6" ht="14" x14ac:dyDescent="0.15">
       <c r="A25" s="6">
         <v>3</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C25" s="24" t="s">
+      <c r="C25" s="23" t="s">
         <v>748</v>
       </c>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+    </row>
+    <row r="26" spans="1:6" ht="14" x14ac:dyDescent="0.15">
       <c r="A26" s="8">
         <v>4</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="C26" s="25" t="s">
+      <c r="C26" s="24" t="s">
         <v>748</v>
       </c>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+    </row>
+    <row r="27" spans="1:6" ht="14" x14ac:dyDescent="0.15">
       <c r="A27" s="2">
         <v>5</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C27" s="22" t="s">
+      <c r="C27" s="21" t="s">
         <v>749</v>
       </c>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+    </row>
+    <row r="28" spans="1:6" ht="14" x14ac:dyDescent="0.15">
       <c r="A28" s="4">
         <v>6</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="C28" s="23" t="s">
+      <c r="C28" s="22" t="s">
         <v>750</v>
       </c>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+    </row>
+    <row r="29" spans="1:6" ht="14" x14ac:dyDescent="0.15">
       <c r="A29" s="6">
         <v>7</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="C29" s="24" t="s">
+      <c r="C29" s="23" t="s">
         <v>751</v>
       </c>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+    </row>
+    <row r="30" spans="1:6" ht="14" x14ac:dyDescent="0.15">
       <c r="A30" s="8">
         <v>8</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="C30" s="25" t="s">
+      <c r="C30" s="24" t="s">
         <v>752</v>
       </c>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+    </row>
+    <row r="31" spans="1:6" ht="14" x14ac:dyDescent="0.15">
       <c r="A31" s="2">
         <v>9</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="C31" s="22" t="s">
+      <c r="C31" s="21" t="s">
         <v>753</v>
       </c>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+    </row>
+    <row r="32" spans="1:6" ht="14" x14ac:dyDescent="0.15">
       <c r="A32" s="4">
         <v>10</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="C32" s="23" t="s">
+      <c r="C32" s="22" t="s">
         <v>754</v>
       </c>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+    </row>
+    <row r="33" spans="1:6" ht="14" x14ac:dyDescent="0.15">
       <c r="A33" s="6">
         <v>11</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="C33" s="24" t="s">
+      <c r="C33" s="23" t="s">
         <v>748</v>
       </c>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+    </row>
+    <row r="34" spans="1:6" ht="14" x14ac:dyDescent="0.15">
       <c r="A34" s="8">
         <v>12</v>
       </c>
       <c r="B34" s="8" t="s">
         <v>342</v>
       </c>
-      <c r="C34" s="25" t="s">
+      <c r="C34" s="24" t="s">
         <v>754</v>
       </c>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+    </row>
+    <row r="35" spans="1:6" ht="14" x14ac:dyDescent="0.15">
       <c r="A35" s="2">
         <v>13</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="C35" s="22" t="s">
+      <c r="C35" s="21" t="s">
         <v>755</v>
       </c>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+    </row>
+    <row r="36" spans="1:6" ht="14" x14ac:dyDescent="0.15">
       <c r="A36" s="4">
         <v>14</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="C36" s="23" t="s">
+      <c r="C36" s="22" t="s">
         <v>754</v>
       </c>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+    </row>
+    <row r="37" spans="1:6" ht="14" x14ac:dyDescent="0.15">
       <c r="A37" s="6">
         <v>15</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>422</v>
       </c>
-      <c r="C37" s="24" t="s">
+      <c r="C37" s="23" t="s">
         <v>756</v>
       </c>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+    </row>
+    <row r="38" spans="1:6" ht="14" x14ac:dyDescent="0.15">
       <c r="A38" s="8">
         <v>16</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>440</v>
       </c>
-      <c r="C38" s="25" t="s">
+      <c r="C38" s="24" t="s">
         <v>747</v>
       </c>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="19"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+    </row>
+    <row r="39" spans="1:6" ht="14" x14ac:dyDescent="0.15">
       <c r="A39" s="2">
         <v>17</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="C39" s="22" t="s">
+      <c r="C39" s="21" t="s">
         <v>757</v>
       </c>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+    </row>
+    <row r="40" spans="1:6" ht="14" x14ac:dyDescent="0.15">
       <c r="A40" s="4">
         <v>18</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>472</v>
       </c>
-      <c r="C40" s="23" t="s">
+      <c r="C40" s="22" t="s">
         <v>757</v>
       </c>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+    </row>
+    <row r="41" spans="1:6" ht="14" x14ac:dyDescent="0.15">
       <c r="A41" s="6">
         <v>19</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>498</v>
       </c>
-      <c r="C41" s="24" t="s">
+      <c r="C41" s="23" t="s">
         <v>753</v>
       </c>
-      <c r="D41" s="19"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D41" s="18"/>
+    </row>
+    <row r="42" spans="1:6" ht="14" x14ac:dyDescent="0.15">
       <c r="A42" s="8">
         <v>20</v>
       </c>
       <c r="B42" s="8" t="s">
         <v>512</v>
       </c>
-      <c r="C42" s="25" t="s">
+      <c r="C42" s="24" t="s">
         <v>753</v>
       </c>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
+    </row>
+    <row r="43" spans="1:6" ht="14" x14ac:dyDescent="0.15">
       <c r="A43" s="2">
         <v>21</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="C43" s="22" t="s">
+      <c r="C43" s="21" t="s">
         <v>756</v>
       </c>
-      <c r="D43" s="19"/>
-      <c r="E43" s="19"/>
-      <c r="F43" s="19"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18"/>
+    </row>
+    <row r="44" spans="1:6" ht="14" x14ac:dyDescent="0.15">
       <c r="A44" s="4">
         <v>22</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>569</v>
       </c>
-      <c r="C44" s="23" t="s">
+      <c r="C44" s="22" t="s">
         <v>754</v>
       </c>
-      <c r="D44" s="19"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="19"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="18"/>
+    </row>
+    <row r="45" spans="1:6" ht="14" x14ac:dyDescent="0.15">
       <c r="A45" s="6">
         <v>23</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>587</v>
       </c>
-      <c r="C45" s="24" t="s">
+      <c r="C45" s="23" t="s">
         <v>748</v>
       </c>
-      <c r="D45" s="19"/>
-      <c r="E45" s="19"/>
-      <c r="F45" s="19"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="18"/>
+    </row>
+    <row r="46" spans="1:6" ht="14" x14ac:dyDescent="0.15">
       <c r="A46" s="8">
         <v>24</v>
       </c>
       <c r="B46" s="8" t="s">
         <v>583</v>
       </c>
-      <c r="C46" s="25" t="s">
+      <c r="C46" s="24" t="s">
         <v>753</v>
       </c>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="19"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D46" s="18"/>
+      <c r="E46" s="18"/>
+      <c r="F46" s="18"/>
+    </row>
+    <row r="47" spans="1:6" ht="14" x14ac:dyDescent="0.15">
       <c r="A47" s="2">
         <v>25</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="C47" s="22" t="s">
+      <c r="C47" s="21" t="s">
         <v>753</v>
       </c>
-      <c r="D47" s="19"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="19"/>
-    </row>
-    <row r="48" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+      <c r="D47" s="18"/>
+      <c r="E47" s="18"/>
+      <c r="F47" s="18"/>
+    </row>
+    <row r="48" spans="1:6" ht="14" x14ac:dyDescent="0.15">
       <c r="A48" s="4">
         <v>26</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>663</v>
       </c>
-      <c r="C48" s="23" t="s">
+      <c r="C48" s="22" t="s">
         <v>758</v>
       </c>
-      <c r="D48" s="19"/>
-      <c r="E48" s="19"/>
-      <c r="F48" s="19"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D48" s="18"/>
+      <c r="E48" s="18"/>
+      <c r="F48" s="18"/>
+    </row>
+    <row r="49" spans="1:6" ht="14" x14ac:dyDescent="0.15">
       <c r="A49" s="6">
         <v>27</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>680</v>
       </c>
-      <c r="C49" s="24" t="s">
+      <c r="C49" s="23" t="s">
         <v>752</v>
       </c>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19"/>
-      <c r="F49" s="19"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="18"/>
+      <c r="F49" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="A21:C21"/>
@@ -7609,11 +7626,18 @@
     <mergeCell ref="D16:F16"/>
     <mergeCell ref="D17:F17"/>
     <mergeCell ref="D18:F18"/>
-    <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="B12:C12"/>
   </mergeCells>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
